--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -39,50 +39,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <si>
     <t>常量键</t>
   </si>
   <si>
+    <t>主键中文翻译</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>备注中文解释</t>
+  </si>
+  <si>
     <t>主键</t>
   </si>
   <si>
+    <t>展示用中文名；运行时不读</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>英文备注；运行时不读</t>
+  </si>
+  <si>
+    <t>中文说明；运行时不读</t>
+  </si>
+  <si>
     <t>ConstantKey</t>
   </si>
   <si>
-    <t>主键中文翻译</t>
-  </si>
-  <si>
-    <t>展示用中文名；运行时不读</t>
-  </si>
-  <si>
     <t>ConstantKeyZh</t>
   </si>
   <si>
-    <t>数值</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>英文备注；运行时不读</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
-    <t>备注中文解释</t>
-  </si>
-  <si>
-    <t>中文说明；运行时不读</t>
-  </si>
-  <si>
     <t>CommentZh</t>
   </si>
   <si>
@@ -107,7 +107,7 @@
     <t>AttackSpeed constant term</t>
   </si>
   <si>
-    <t>攻速=本值+AttackSpeedAgiDiv/max(敏捷,1)中的常数项</t>
+    <t>攻速=本值+敏捷相关项中的常数项</t>
   </si>
   <si>
     <t>AttackSpeedAgiDiv</t>
@@ -156,6 +156,594 @@
   </si>
   <si>
     <t>士兵最大生命=ceil(躯体生命+力量×本系数)</t>
+  </si>
+  <si>
+    <t>CameraHeightY</t>
+  </si>
+  <si>
+    <t>镜头高度</t>
+  </si>
+  <si>
+    <t>Top-down camera world Y above map center</t>
+  </si>
+  <si>
+    <t>俯视正交相机相对地图中心的世界Y高度；Dig/Defend/布阵/PushMap共用</t>
+  </si>
+  <si>
+    <t>CameraOrthoSizeMargin</t>
+  </si>
+  <si>
+    <t>地图适配Size余量</t>
+  </si>
+  <si>
+    <t>orthoSize = max(halfExtents) - margin</t>
+  </si>
+  <si>
+    <t>Dig/Defend/布阵：正交Size=地图半幅较大边减去本余量</t>
+  </si>
+  <si>
+    <t>PushMapCameraOrthoSize</t>
+  </si>
+  <si>
+    <t>推图开战默认Size</t>
+  </si>
+  <si>
+    <t>PushMap combat default orthographicSize</t>
+  </si>
+  <si>
+    <t>PushMap开战默认正交Size（异于Defend的地图适配公式）</t>
+  </si>
+  <si>
+    <t>CameraNearClip</t>
+  </si>
+  <si>
+    <t>镜头近裁剪面</t>
+  </si>
+  <si>
+    <t>Camera nearClipPlane</t>
+  </si>
+  <si>
+    <t>正交相机近裁剪面</t>
+  </si>
+  <si>
+    <t>CameraFarClip</t>
+  </si>
+  <si>
+    <t>镜头远裁剪面</t>
+  </si>
+  <si>
+    <t>Camera farClipPlane</t>
+  </si>
+  <si>
+    <t>正交相机远裁剪面</t>
+  </si>
+  <si>
+    <t>CameraFollowDeadzone</t>
+  </si>
+  <si>
+    <t>跟随死区半径</t>
+  </si>
+  <si>
+    <t>PushMap Auto follow deadzone world-XZ</t>
+  </si>
+  <si>
+    <t>PushMap Auto跟随：目标在死区内则镜头XZ不移动</t>
+  </si>
+  <si>
+    <t>CameraFollowSmoothTime</t>
+  </si>
+  <si>
+    <t>跟随平滑时间</t>
+  </si>
+  <si>
+    <t>PushMap Auto SmoothDamp time</t>
+  </si>
+  <si>
+    <t>PushMap Auto跟随：超出死区后XZ SmoothDamp时间（秒）</t>
+  </si>
+  <si>
+    <t>CameraZoomStepPerNotch</t>
+  </si>
+  <si>
+    <t>滚轮缩放步进</t>
+  </si>
+  <si>
+    <t>Scroll wheel orthographicSize step</t>
+  </si>
+  <si>
+    <t>PushMap滚轮每格改变的正交Size</t>
+  </si>
+  <si>
+    <t>CameraOrthoSizeMin</t>
+  </si>
+  <si>
+    <t>正交Size下限</t>
+  </si>
+  <si>
+    <t>Min orthographicSize clamp</t>
+  </si>
+  <si>
+    <t>正交Size下限（含Dig/Defend适配结果钳制与PushMap缩放）</t>
+  </si>
+  <si>
+    <t>CameraOrthoSizeMax</t>
+  </si>
+  <si>
+    <t>正交Size上限</t>
+  </si>
+  <si>
+    <t>Max orthographicSize clamp</t>
+  </si>
+  <si>
+    <t>PushMap滚轮缩放上限</t>
+  </si>
+  <si>
+    <t>CameraDragThresholdPixels</t>
+  </si>
+  <si>
+    <t>拖拽启动像素阈值</t>
+  </si>
+  <si>
+    <t>LMB drag arm threshold in screen px</t>
+  </si>
+  <si>
+    <t>PushMap手动拖镜头：累计位移超过本像素才开始平移</t>
+  </si>
+  <si>
+    <t>PushMapCameraIntroSpeed</t>
+  </si>
+  <si>
+    <t>推图镜头预览速度</t>
+  </si>
+  <si>
+    <t>PushMap StartBattle Intro rail speed world-XZ units/sec</t>
+  </si>
+  <si>
+    <t>PushMap开战镜头预览沿CameraFollowPath的世界XZ恒速（单位/秒）</t>
+  </si>
+  <si>
+    <t>PushMapCameraIntroWaypointDwellSeconds</t>
+  </si>
+  <si>
+    <t>推图镜头预览路点停留</t>
+  </si>
+  <si>
+    <t>PushMap Intro dwell seconds at each author WP</t>
+  </si>
+  <si>
+    <t>PushMap开战镜头预览在每个作者路点（含起终点）的停留秒数</t>
+  </si>
+  <si>
+    <t>DigTriggerDwellSeconds</t>
+  </si>
+  <si>
+    <t>挖坟触发停留</t>
+  </si>
+  <si>
+    <t>Cursor dwell before DigAction starts</t>
+  </si>
+  <si>
+    <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
+  </si>
+  <si>
+    <t>BaseDigDuration</t>
+  </si>
+  <si>
+    <t>挖坟基础时长</t>
+  </si>
+  <si>
+    <t>BaseDigDuration seconds</t>
+  </si>
+  <si>
+    <t>DigActionDuration=max(下限</t>
+  </si>
+  <si>
+    <t>DigActionDurationFloor</t>
+  </si>
+  <si>
+    <t>挖坟最短时长</t>
+  </si>
+  <si>
+    <t>Min DigActionDuration seconds</t>
+  </si>
+  <si>
+    <t>单次挖坟最短秒数（公式地板）</t>
+  </si>
+  <si>
+    <t>AttackSlotMeleeCount</t>
+  </si>
+  <si>
+    <t>近战攻击位数量</t>
+  </si>
+  <si>
+    <t>Melee AttackSlot ring slot count</t>
+  </si>
+  <si>
+    <t>近战单位围绕目标可占用的攻击位数量</t>
+  </si>
+  <si>
+    <t>AttackSlotRangedCount</t>
+  </si>
+  <si>
+    <t>远程攻击位数量</t>
+  </si>
+  <si>
+    <t>Ranged AttackSlot ring slot count</t>
+  </si>
+  <si>
+    <t>远程单位围绕目标可占用的攻击位数量</t>
+  </si>
+  <si>
+    <t>AttackSlotMargin</t>
+  </si>
+  <si>
+    <t>攻击位环半径余量</t>
+  </si>
+  <si>
+    <t>Ring radius = reach sum - margin</t>
+  </si>
+  <si>
+    <t>攻击位环半径计算时从可达距离减去的余量</t>
+  </si>
+  <si>
+    <t>AttackSlotMinRingRadius</t>
+  </si>
+  <si>
+    <t>攻击位环最小半径</t>
+  </si>
+  <si>
+    <t>Min AttackSlot ring radius</t>
+  </si>
+  <si>
+    <t>攻击位环半径下限</t>
+  </si>
+  <si>
+    <t>AttackSlotReclaimMoveThreshold</t>
+  </si>
+  <si>
+    <t>攻击位重算位移阈值</t>
+  </si>
+  <si>
+    <t>Target move distance to recompute slots</t>
+  </si>
+  <si>
+    <t>目标移动超过本距离时重算攻击位</t>
+  </si>
+  <si>
+    <t>AttackSlotDefaultTargetBodyRadius</t>
+  </si>
+  <si>
+    <t>默认目标体半径</t>
+  </si>
+  <si>
+    <t>Fallback target BodyRadius</t>
+  </si>
+  <si>
+    <t>缺体外观/怪物半径时的默认目标体半径</t>
+  </si>
+  <si>
+    <t>HitConfirmSlack</t>
+  </si>
+  <si>
+    <t>命中确认松弛距离</t>
+  </si>
+  <si>
+    <t>HitConfirm range slack</t>
+  </si>
+  <si>
+    <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
+  </si>
+  <si>
+    <t>SurroundGapDegrees</t>
+  </si>
+  <si>
+    <t>包围缺口角度</t>
+  </si>
+  <si>
+    <t>Surround gap sector degrees</t>
+  </si>
+  <si>
+    <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
+  </si>
+  <si>
+    <t>StuckDetectWindowSeconds</t>
+  </si>
+  <si>
+    <t>卡死检测窗口</t>
+  </si>
+  <si>
+    <t>StuckHold detect window seconds</t>
+  </si>
+  <si>
+    <t>有移动意图但位移不足时的检测窗口秒数</t>
+  </si>
+  <si>
+    <t>StuckDisplacementEpsilon</t>
+  </si>
+  <si>
+    <t>卡死位移阈值</t>
+  </si>
+  <si>
+    <t>StuckHold displacement epsilon</t>
+  </si>
+  <si>
+    <t>检测窗口内XZ位移小于本值则判定卡住</t>
+  </si>
+  <si>
+    <t>StuckHoldSeconds</t>
+  </si>
+  <si>
+    <t>卡死停顿时长</t>
+  </si>
+  <si>
+    <t>StuckHold force-Idle seconds</t>
+  </si>
+  <si>
+    <t>判定卡住后强制Idle的秒数</t>
+  </si>
+  <si>
+    <t>ProjectileDefaultHitRadius</t>
+  </si>
+  <si>
+    <t>投射物默认命中半径</t>
+  </si>
+  <si>
+    <t>Default projectile soft-hit radius</t>
+  </si>
+  <si>
+    <t>远程投射物默认软命中半径（表缺列时兜底）</t>
+  </si>
+  <si>
+    <t>DefendVictoryStageExp</t>
+  </si>
+  <si>
+    <t>防守胜利阶段经验</t>
+  </si>
+  <si>
+    <t>Defend victory Demo stage Exp</t>
+  </si>
+  <si>
+    <t>Defend清场胜利结算时入账的阶段经验</t>
+  </si>
+  <si>
+    <t>FlowFieldDefaultCellSize</t>
+  </si>
+  <si>
+    <t>流场默认格宽</t>
+  </si>
+  <si>
+    <t>FlowField default cell size</t>
+  </si>
+  <si>
+    <t>共享目标流场默认格子边长</t>
+  </si>
+  <si>
+    <t>FlowFieldMinCellSize</t>
+  </si>
+  <si>
+    <t>流场最小格宽</t>
+  </si>
+  <si>
+    <t>FlowField min cell size</t>
+  </si>
+  <si>
+    <t>流场格宽下限（性能降级时可抬高）</t>
+  </si>
+  <si>
+    <t>FlowFieldMaxCellSize</t>
+  </si>
+  <si>
+    <t>流场最大格宽</t>
+  </si>
+  <si>
+    <t>FlowField max cell size</t>
+  </si>
+  <si>
+    <t>流场格宽上限</t>
+  </si>
+  <si>
+    <t>MassMoveMaxRecalcPerFrame</t>
+  </si>
+  <si>
+    <t>群体移动每帧重算上限</t>
+  </si>
+  <si>
+    <t>MassMove/AttackSlot refresh budget per frame</t>
+  </si>
+  <si>
+    <t>每帧最多重算路径/攻击位的单位数</t>
+  </si>
+  <si>
+    <t>MassMoveDefaultAgentRadius</t>
+  </si>
+  <si>
+    <t>群体移动默认体半径</t>
+  </si>
+  <si>
+    <t>Default mass-move agent radius</t>
+  </si>
+  <si>
+    <t>群体移动登记时的默认体半径</t>
+  </si>
+  <si>
+    <t>MassMoveArriveEpsilon</t>
+  </si>
+  <si>
+    <t>群体移动到达阈值</t>
+  </si>
+  <si>
+    <t>Arrive epsilon for DesiredDestination</t>
+  </si>
+  <si>
+    <t>到达期望点判定的距离阈值</t>
+  </si>
+  <si>
+    <t>MassMoveDefaultObjectiveArriveRadius</t>
+  </si>
+  <si>
+    <t>目标到达默认半径</t>
+  </si>
+  <si>
+    <t>Default Objective arrive radius</t>
+  </si>
+  <si>
+    <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
+  </si>
+  <si>
+    <t>MassMoveAttackSlotSeparationScale</t>
+  </si>
+  <si>
+    <t>攻击位软分离系数</t>
+  </si>
+  <si>
+    <t>LocalDetour separation scale in AttackSlot</t>
+  </si>
+  <si>
+    <t>处于攻击位气泡时LocalDetour软分离缩放</t>
+  </si>
+  <si>
+    <t>SoftCollisionMaxCorrectionSpeed</t>
+  </si>
+  <si>
+    <t>软碰撞最大修正速度</t>
+  </si>
+  <si>
+    <t>Soft collision max correction speed</t>
+  </si>
+  <si>
+    <t>软碰撞位置修正速度上限（单位/秒）</t>
+  </si>
+  <si>
+    <t>LocalDetourProbeLength</t>
+  </si>
+  <si>
+    <t>本地绕行探测长度</t>
+  </si>
+  <si>
+    <t>LocalDetour L/R probe length</t>
+  </si>
+  <si>
+    <t>左右绕行探测射线长度</t>
+  </si>
+  <si>
+    <t>LocalDetourSoftSeparationStrength</t>
+  </si>
+  <si>
+    <t>本地绕行软分离强度</t>
+  </si>
+  <si>
+    <t>LocalDetour soft separation strength</t>
+  </si>
+  <si>
+    <t>友军软分离推力强度</t>
+  </si>
+  <si>
+    <t>LocalDetourDetourBias</t>
+  </si>
+  <si>
+    <t>本地绕行偏置</t>
+  </si>
+  <si>
+    <t>LocalDetour L/R bias blend</t>
+  </si>
+  <si>
+    <t>绕行方向与原期望方向的混合偏置</t>
+  </si>
+  <si>
+    <t>LocalDetourForwardConeHalfAngleDeg</t>
+  </si>
+  <si>
+    <t>本地绕行前向锥半角</t>
+  </si>
+  <si>
+    <t>Forward block cone half-angle degrees</t>
+  </si>
+  <si>
+    <t>判定前方友军阻挡的圆锥半角（度）</t>
+  </si>
+  <si>
+    <t>BossAdvanceArriveRadius</t>
+  </si>
+  <si>
+    <t>Boss推进到达半径</t>
+  </si>
+  <si>
+    <t>BossPoint advance arrive radius</t>
+  </si>
+  <si>
+    <t>目标链耗尽后推进Boss点的到达半径</t>
+  </si>
+  <si>
+    <t>EngageStickHysteresisMargin</t>
+  </si>
+  <si>
+    <t>接战粘滞余量</t>
+  </si>
+  <si>
+    <t>Engage sticky retarget hysteresis</t>
+  </si>
+  <si>
+    <t>接战粘滞：新目标需更近超过本余量才换目标</t>
+  </si>
+  <si>
+    <t>PushMapSpawnMinSampleDistance</t>
+  </si>
+  <si>
+    <t>刷怪散布最小采样距</t>
+  </si>
+  <si>
+    <t>PushMap spawn min sample distance</t>
+  </si>
+  <si>
+    <t>刷怪散布环形采样的最小间距</t>
+  </si>
+  <si>
+    <t>PushMapSpawnSampleDistanceBodyMul</t>
+  </si>
+  <si>
+    <t>刷怪散布体半径倍数</t>
+  </si>
+  <si>
+    <t>Spawn sample distance = max(min</t>
+  </si>
+  <si>
+    <t>r*mul)</t>
+  </si>
+  <si>
+    <t>PushMapSpawnLeashSlack</t>
+  </si>
+  <si>
+    <t>刷怪拴绳松弛</t>
+  </si>
+  <si>
+    <t>NavMesh sample leash slack</t>
+  </si>
+  <si>
+    <t>刷怪SamplePosition相对基点的拴绳松弛</t>
+  </si>
+  <si>
+    <t>PushMapSpawnAbsoluteLeashFloor</t>
+  </si>
+  <si>
+    <t>刷怪绝对拴绳下限</t>
+  </si>
+  <si>
+    <t>Absolute leash floor</t>
+  </si>
+  <si>
+    <t>刷怪绝对拴绳距离下限</t>
+  </si>
+  <si>
+    <t>PushMapSpawnAbsoluteLeashBodyMul</t>
+  </si>
+  <si>
+    <t>刷怪绝对拴绳体倍数</t>
+  </si>
+  <si>
+    <t>Absolute leash = max(floor</t>
+  </si>
+  <si>
+    <t>r*mul)</t>
   </si>
 </sst>
 </file>
@@ -538,62 +1126,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152188F9-B4F1-4AA8-8C2D-95D7862DEBAB}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -610,7 +1198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -627,7 +1215,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -644,7 +1232,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -661,7 +1249,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -678,7 +1266,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -695,8 +1283,839 @@
         <v>38</v>
       </c>
     </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11">
+        <v>1.5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15">
+        <v>0.15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16">
+        <v>0.25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17">
+        <v>0.5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18">
+        <v>0.5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21">
+        <v>1.5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22">
+        <v>0.5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23">
+        <v>0.2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24">
+        <v>0.8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>0.1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28">
+        <v>0.05</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29">
+        <v>0.05</v>
+      </c>
+      <c r="D29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30">
+        <v>0.5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31">
+        <v>0.35</v>
+      </c>
+      <c r="D31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32">
+        <v>0.05</v>
+      </c>
+      <c r="D32" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33">
+        <v>60</v>
+      </c>
+      <c r="D33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>135</v>
+      </c>
+      <c r="B34" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34">
+        <v>0.5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>139</v>
+      </c>
+      <c r="B35" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35">
+        <v>0.2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37">
+        <v>0.55</v>
+      </c>
+      <c r="D37" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38">
+        <v>100</v>
+      </c>
+      <c r="D38" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>155</v>
+      </c>
+      <c r="B39" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39">
+        <v>0.5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" t="s">
+        <v>160</v>
+      </c>
+      <c r="C40">
+        <v>0.25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B41" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41">
+        <v>0.5</v>
+      </c>
+      <c r="D41" t="s">
+        <v>165</v>
+      </c>
+      <c r="E41" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42">
+        <v>50</v>
+      </c>
+      <c r="D42" t="s">
+        <v>169</v>
+      </c>
+      <c r="E42" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>171</v>
+      </c>
+      <c r="B43" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43">
+        <v>0.1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44">
+        <v>0.08</v>
+      </c>
+      <c r="D44" t="s">
+        <v>177</v>
+      </c>
+      <c r="E44" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" t="s">
+        <v>180</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" t="s">
+        <v>184</v>
+      </c>
+      <c r="C46">
+        <v>0.35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>185</v>
+      </c>
+      <c r="E46" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>189</v>
+      </c>
+      <c r="E47" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>191</v>
+      </c>
+      <c r="B48" t="s">
+        <v>192</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>193</v>
+      </c>
+      <c r="E48" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>195</v>
+      </c>
+      <c r="B49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49">
+        <v>0.15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>197</v>
+      </c>
+      <c r="E49" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50">
+        <v>0.85</v>
+      </c>
+      <c r="D50" t="s">
+        <v>201</v>
+      </c>
+      <c r="E50" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>203</v>
+      </c>
+      <c r="B51" t="s">
+        <v>204</v>
+      </c>
+      <c r="C51">
+        <v>50</v>
+      </c>
+      <c r="D51" t="s">
+        <v>205</v>
+      </c>
+      <c r="E51" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52">
+        <v>0.35</v>
+      </c>
+      <c r="D52" t="s">
+        <v>209</v>
+      </c>
+      <c r="E52" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>211</v>
+      </c>
+      <c r="B53" t="s">
+        <v>212</v>
+      </c>
+      <c r="C53">
+        <v>0.15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>213</v>
+      </c>
+      <c r="E53" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>215</v>
+      </c>
+      <c r="B54" t="s">
+        <v>216</v>
+      </c>
+      <c r="C54">
+        <v>0.75</v>
+      </c>
+      <c r="D54" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>219</v>
+      </c>
+      <c r="B55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C55">
+        <v>2.5</v>
+      </c>
+      <c r="D55" t="s">
+        <v>221</v>
+      </c>
+      <c r="E55" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>223</v>
+      </c>
+      <c r="B56" t="s">
+        <v>224</v>
+      </c>
+      <c r="C56">
+        <v>0.35</v>
+      </c>
+      <c r="D56" t="s">
+        <v>225</v>
+      </c>
+      <c r="E56" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" t="s">
+        <v>228</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>229</v>
+      </c>
+      <c r="E57" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>231</v>
+      </c>
+      <c r="B58" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58">
+        <v>10</v>
+      </c>
+      <c r="D58" t="s">
+        <v>233</v>
+      </c>
+      <c r="E58" t="s">
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,25 +766,25 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>PushMapPrepareOrthoSize</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>推图布阵默认Size</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>PushMap Prepare FormationCamera orthographicSize (not map-fit)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>PushMap Prepare 布阵 FormationCamera 正交Size（不用地图适配公式）</t>
         </is>
@@ -1937,6 +1937,81 @@
       <c r="E59" s="0" t="inlineStr">
         <is>
           <t>r*mul)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t>DeathKnockbackRatioCoeff</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>死亡击飞比例系数</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>Knockback raw=(MaxHp/OutgoingDamage)*Coeff</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>击飞距离raw=(MaxHp/OutgoingDamage)×本系数；再clamp到Min/Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t>DeathKnockbackMinDistance</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>死亡击飞最小距离</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>Death knockback distance floor</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>怪物死亡击飞距离下限（世界单位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t>DeathKnockbackMaxDistance</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>死亡击飞最大距离</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>Death knockback distance ceiling</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
         </is>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -2,34 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -51,19 +44,15 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -136,7 +125,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -146,44 +135,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -210,32 +199,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -262,24 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -291,162 +244,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -456,1562 +413,1707 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>常量键</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>主键中文翻译</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>备注中文解释</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ConstantKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ConstantKeyZh</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CommentZh</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>展示用中文名；运行时不读</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>英文备注；运行时不读</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>中文说明；运行时不读</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）ConstantKey</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）ConstantKeyZh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）Value</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）Comment</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）CommentZh</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ConstantKey</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ConstantKeyZh</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>CommentZh</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>普攻主属性倍率</t>
         </is>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>NormalAttackPower = Primary x Mult</t>
         </is>
       </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>普通攻击伤害=主属性最终值×本系数；职业表CombatConvertCoeffs可覆盖</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>AttackSpeedBase</t>
         </is>
       </c>
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>攻击速度基础值</t>
         </is>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>AttackSpeed constant term</t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>攻速=本值+敏捷相关项中的常数项</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>AttackSpeedAgiDiv</t>
         </is>
       </c>
-      <c r="B6" s="0" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>攻击速度敏捷除数</t>
         </is>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>60</v>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>AttackSpeed Agility divisor</t>
         </is>
       </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>攻速公式中除以敏捷的分子；敏捷越高攻速越接近基础值</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>SkillCdIntDiv</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>技能冷却智力除数</t>
         </is>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>SkillCooldown Intelligence divisor</t>
         </is>
       </c>
-      <c r="E7" s="0" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>技能CD=max(下限,基础CD−本值/max(智力,1))；Demo不施放</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>SkillCdFloor</t>
         </is>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>技能冷却下限</t>
         </is>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>SkillCooldown floor seconds</t>
         </is>
       </c>
-      <c r="E8" s="0" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>技能冷却最短秒数，防止智力过高使CD过低</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>MaxHpStrengthMult</t>
         </is>
       </c>
-      <c r="B9" s="0" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>血量力量系数</t>
         </is>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>MaxHP = ceil(BodyLife + Str x Mult)</t>
         </is>
       </c>
-      <c r="E9" s="0" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>士兵最大生命=ceil(躯体生命+力量×本系数)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>CameraHeightY</t>
         </is>
       </c>
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>镜头高度</t>
         </is>
       </c>
-      <c r="C10" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Top-down camera world Y above map center</t>
         </is>
       </c>
-      <c r="E10" s="0" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>俯视正交相机相对地图中心的世界Y高度；Dig/Defend/布阵/PushMap共用</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CameraOrthoSizeMargin</t>
         </is>
       </c>
-      <c r="B11" s="0" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>地图适配Size余量</t>
         </is>
       </c>
-      <c r="C11" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>orthoSize = max(halfExtents) - margin</t>
         </is>
       </c>
-      <c r="E11" s="0" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Dig/Defend/布阵：正交Size=地图半幅较大边减去本余量</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>PushMapCameraOrthoSize</t>
         </is>
       </c>
-      <c r="B12" s="0" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>推图开战默认Size</t>
         </is>
       </c>
-      <c r="C12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="0" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>PushMap combat default orthographicSize</t>
         </is>
       </c>
-      <c r="E12" s="0" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>PushMap开战默认正交Size（异于Defend的地图适配公式）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>PushMapPrepareOrthoSize</t>
         </is>
       </c>
-      <c r="B13" s="0" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>推图布阵默认Size</t>
         </is>
       </c>
-      <c r="C13" s="0" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D13" s="0" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>PushMap Prepare FormationCamera orthographicSize (not map-fit)</t>
         </is>
       </c>
-      <c r="E13" s="0" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>PushMap Prepare 布阵 FormationCamera 正交Size（不用地图适配公式）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>CameraNearClip</t>
         </is>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>镜头近裁剪面</t>
         </is>
       </c>
-      <c r="C14" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D14" s="0" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Camera nearClipPlane</t>
         </is>
       </c>
-      <c r="E14" s="0" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>正交相机近裁剪面</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>CameraFarClip</t>
         </is>
       </c>
-      <c r="B15" s="0" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>镜头远裁剪面</t>
         </is>
       </c>
-      <c r="C15" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" s="0" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Camera farClipPlane</t>
         </is>
       </c>
-      <c r="E15" s="0" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>正交相机远裁剪面</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>CameraFollowDeadzone</t>
         </is>
       </c>
-      <c r="B16" s="0" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>跟随死区半径</t>
         </is>
       </c>
-      <c r="C16" s="0" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D16" s="0" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>PushMap Auto follow deadzone world-XZ</t>
         </is>
       </c>
-      <c r="E16" s="0" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>PushMap Auto跟随：目标在死区内则镜头XZ不移动</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>CameraFollowSmoothTime</t>
         </is>
       </c>
-      <c r="B17" s="0" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>跟随平滑时间</t>
         </is>
       </c>
-      <c r="C17" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D17" s="0" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>PushMap Auto SmoothDamp time</t>
         </is>
       </c>
-      <c r="E17" s="0" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>PushMap Auto跟随：超出死区后XZ SmoothDamp时间（秒）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>CameraZoomStepPerNotch</t>
         </is>
       </c>
-      <c r="B18" s="0" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>滚轮缩放步进</t>
         </is>
       </c>
-      <c r="C18" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D18" s="0" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Scroll wheel orthographicSize step</t>
         </is>
       </c>
-      <c r="E18" s="0" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>PushMap滚轮每格改变的正交Size</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="0" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>CameraOrthoSizeMin</t>
         </is>
       </c>
-      <c r="B19" s="0" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>正交Size下限</t>
         </is>
       </c>
-      <c r="C19" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D19" s="0" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Min orthographicSize clamp</t>
         </is>
       </c>
-      <c r="E19" s="0" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>正交Size下限（含Dig/Defend适配结果钳制与PushMap缩放）</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="0" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>CameraOrthoSizeMax</t>
         </is>
       </c>
-      <c r="B20" s="0" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>正交Size上限</t>
         </is>
       </c>
-      <c r="C20" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="D20" s="0" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Max orthographicSize clamp</t>
         </is>
       </c>
-      <c r="E20" s="0" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>PushMap滚轮缩放上限</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="0" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>CameraDragThresholdPixels</t>
         </is>
       </c>
-      <c r="B21" s="0" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>拖拽启动像素阈值</t>
         </is>
       </c>
-      <c r="C21" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>LMB drag arm threshold in screen px</t>
         </is>
       </c>
-      <c r="E21" s="0" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>PushMap手动拖镜头：累计位移超过本像素才开始平移</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="0" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>PushMapCameraIntroSpeed</t>
         </is>
       </c>
-      <c r="B22" s="0" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>推图镜头预览速度</t>
         </is>
       </c>
-      <c r="C22" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>PushMap StartBattle Intro rail speed world-XZ units/sec</t>
         </is>
       </c>
-      <c r="E22" s="0" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>PushMap开战镜头预览沿CameraFollowPath的世界XZ恒速（单位/秒）</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="0" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>PushMapCameraIntroWaypointDwellSeconds</t>
         </is>
       </c>
-      <c r="B23" s="0" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>推图镜头预览路点停留</t>
         </is>
       </c>
-      <c r="C23" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D23" s="0" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>PushMap Intro dwell seconds at each author WP</t>
         </is>
       </c>
-      <c r="E23" s="0" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>PushMap开战镜头预览在每个作者路点（含起终点）的停留秒数</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="0" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>DigTriggerDwellSeconds</t>
         </is>
       </c>
-      <c r="B24" s="0" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>挖坟触发停留</t>
         </is>
       </c>
-      <c r="C24" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D24" s="0" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Cursor dwell before DigAction starts</t>
         </is>
       </c>
-      <c r="E24" s="0" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="0" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>BaseDigDuration</t>
         </is>
       </c>
-      <c r="B25" s="0" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>挖坟基础时长</t>
         </is>
       </c>
-      <c r="C25" s="0" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D25" s="0" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>BaseDigDuration seconds</t>
         </is>
       </c>
-      <c r="E25" s="0" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>DigActionDuration=max(下限</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="0" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>DigActionDurationFloor</t>
         </is>
       </c>
-      <c r="B26" s="0" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>挖坟最短时长</t>
         </is>
       </c>
-      <c r="C26" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D26" s="0" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Min DigActionDuration seconds</t>
         </is>
       </c>
-      <c r="E26" s="0" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>单次挖坟最短秒数（公式地板）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="0" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>AttackSlotMeleeCount</t>
         </is>
       </c>
-      <c r="B27" s="0" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>近战攻击位数量</t>
         </is>
       </c>
-      <c r="C27" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Melee AttackSlot ring slot count</t>
         </is>
       </c>
-      <c r="E27" s="0" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>近战单位围绕目标可占用的攻击位数量</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="0" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>AttackSlotRangedCount</t>
         </is>
       </c>
-      <c r="B28" s="0" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>远程攻击位数量</t>
         </is>
       </c>
-      <c r="C28" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D28" s="0" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Ranged AttackSlot ring slot count</t>
         </is>
       </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>远程单位围绕目标可占用的攻击位数量</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="0" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>AttackSlotMargin</t>
         </is>
       </c>
-      <c r="B29" s="0" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>攻击位环半径余量</t>
         </is>
       </c>
-      <c r="C29" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D29" s="0" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Ring radius = reach sum - margin</t>
         </is>
       </c>
-      <c r="E29" s="0" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>攻击位环半径计算时从可达距离减去的余量</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="0" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>AttackSlotMinRingRadius</t>
         </is>
       </c>
-      <c r="B30" s="0" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>攻击位环最小半径</t>
         </is>
       </c>
-      <c r="C30" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D30" s="0" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Min AttackSlot ring radius</t>
         </is>
       </c>
-      <c r="E30" s="0" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>攻击位环半径下限</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="0" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>AttackSlotReclaimMoveThreshold</t>
         </is>
       </c>
-      <c r="B31" s="0" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>攻击位重算位移阈值</t>
         </is>
       </c>
-      <c r="C31" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Target move distance to recompute slots</t>
         </is>
       </c>
-      <c r="E31" s="0" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>目标移动超过本距离时重算攻击位</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="0" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>AttackSlotDefaultTargetBodyRadius</t>
         </is>
       </c>
-      <c r="B32" s="0" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>默认目标体半径</t>
         </is>
       </c>
-      <c r="C32" s="0" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Fallback target BodyRadius</t>
         </is>
       </c>
-      <c r="E32" s="0" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>缺体外观/怪物半径时的默认目标体半径</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="0" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>HitConfirmSlack</t>
         </is>
       </c>
-      <c r="B33" s="0" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>命中确认松弛距离</t>
         </is>
       </c>
-      <c r="C33" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>HitConfirm range slack</t>
         </is>
       </c>
-      <c r="E33" s="0" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="0" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>SurroundGapDegrees</t>
         </is>
       </c>
-      <c r="B34" s="0" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>包围缺口角度</t>
         </is>
       </c>
-      <c r="C34" s="0" t="n">
-        <v>60</v>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Surround gap sector degrees</t>
         </is>
       </c>
-      <c r="E34" s="0" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="0" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>StuckDetectWindowSeconds</t>
         </is>
       </c>
-      <c r="B35" s="0" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>卡死检测窗口</t>
         </is>
       </c>
-      <c r="C35" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D35" s="0" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>StuckHold detect window seconds</t>
         </is>
       </c>
-      <c r="E35" s="0" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>有移动意图但位移不足时的检测窗口秒数</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="0" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>StuckDisplacementEpsilon</t>
         </is>
       </c>
-      <c r="B36" s="0" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>卡死位移阈值</t>
         </is>
       </c>
-      <c r="C36" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D36" s="0" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>StuckHold displacement epsilon</t>
         </is>
       </c>
-      <c r="E36" s="0" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>检测窗口内XZ位移小于本值则判定卡住</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="0" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>StuckHoldSeconds</t>
         </is>
       </c>
-      <c r="B37" s="0" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>卡死停顿时长</t>
         </is>
       </c>
-      <c r="C37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="0" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>StuckHold force-Idle seconds</t>
         </is>
       </c>
-      <c r="E37" s="0" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>判定卡住后强制Idle的秒数</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="0" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>ProjectileDefaultHitRadius</t>
         </is>
       </c>
-      <c r="B38" s="0" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>投射物默认命中半径</t>
         </is>
       </c>
-      <c r="C38" s="0" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D38" s="0" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Default projectile soft-hit radius</t>
         </is>
       </c>
-      <c r="E38" s="0" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>远程投射物默认软命中半径（表缺列时兜底）</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="0" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>DefendVictoryStageExp</t>
         </is>
       </c>
-      <c r="B39" s="0" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>防守胜利阶段经验</t>
         </is>
       </c>
-      <c r="C39" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="D39" s="0" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Defend victory Demo stage Exp</t>
         </is>
       </c>
-      <c r="E39" s="0" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Defend清场胜利结算时入账的阶段经验</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="0" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>FlowFieldDefaultCellSize</t>
         </is>
       </c>
-      <c r="B40" s="0" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>流场默认格宽</t>
         </is>
       </c>
-      <c r="C40" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>FlowField default cell size</t>
         </is>
       </c>
-      <c r="E40" s="0" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>共享目标流场默认格子边长</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="0" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>FlowFieldMinCellSize</t>
         </is>
       </c>
-      <c r="B41" s="0" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>流场最小格宽</t>
         </is>
       </c>
-      <c r="C41" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>FlowField min cell size</t>
         </is>
       </c>
-      <c r="E41" s="0" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>流场格宽下限（性能降级时可抬高）</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="0" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>FlowFieldMaxCellSize</t>
         </is>
       </c>
-      <c r="B42" s="0" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>流场最大格宽</t>
         </is>
       </c>
-      <c r="C42" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D42" s="0" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>FlowField max cell size</t>
         </is>
       </c>
-      <c r="E42" s="0" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>流场格宽上限</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="0" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>MassMoveMaxRecalcPerFrame</t>
         </is>
       </c>
-      <c r="B43" s="0" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>群体移动每帧重算上限</t>
         </is>
       </c>
-      <c r="C43" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>MassMove/AttackSlot refresh budget per frame</t>
         </is>
       </c>
-      <c r="E43" s="0" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>每帧最多重算路径/攻击位的单位数</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="0" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>MassMoveDefaultAgentRadius</t>
         </is>
       </c>
-      <c r="B44" s="0" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>群体移动默认体半径</t>
         </is>
       </c>
-      <c r="C44" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D44" s="0" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Default mass-move agent radius</t>
         </is>
       </c>
-      <c r="E44" s="0" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>群体移动登记时的默认体半径</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="0" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>MassMoveArriveEpsilon</t>
         </is>
       </c>
-      <c r="B45" s="0" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>群体移动到达阈值</t>
         </is>
       </c>
-      <c r="C45" s="0" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D45" s="0" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>Arrive epsilon for DesiredDestination</t>
         </is>
       </c>
-      <c r="E45" s="0" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>到达期望点判定的距离阈值</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="0" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>MassMoveDefaultObjectiveArriveRadius</t>
         </is>
       </c>
-      <c r="B46" s="0" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>目标到达默认半径</t>
         </is>
       </c>
-      <c r="C46" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" s="0" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Default Objective arrive radius</t>
         </is>
       </c>
-      <c r="E46" s="0" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="0" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>MassMoveAttackSlotSeparationScale</t>
         </is>
       </c>
-      <c r="B47" s="0" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>攻击位软分离系数</t>
         </is>
       </c>
-      <c r="C47" s="0" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D47" s="0" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>LocalDetour separation scale in AttackSlot</t>
         </is>
       </c>
-      <c r="E47" s="0" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>处于攻击位气泡时LocalDetour软分离缩放</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="0" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>SoftCollisionMaxCorrectionSpeed</t>
         </is>
       </c>
-      <c r="B48" s="0" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>软碰撞最大修正速度</t>
         </is>
       </c>
-      <c r="C48" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="0" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>Soft collision max correction speed</t>
         </is>
       </c>
-      <c r="E48" s="0" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>软碰撞位置修正速度上限（单位/秒）</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="0" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>LocalDetourProbeLength</t>
         </is>
       </c>
-      <c r="B49" s="0" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>本地绕行探测长度</t>
         </is>
       </c>
-      <c r="C49" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="0" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>LocalDetour L/R probe length</t>
         </is>
       </c>
-      <c r="E49" s="0" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>左右绕行探测射线长度</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="0" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>LocalDetourSoftSeparationStrength</t>
         </is>
       </c>
-      <c r="B50" s="0" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>本地绕行软分离强度</t>
         </is>
       </c>
-      <c r="C50" s="0" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D50" s="0" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>LocalDetour soft separation strength</t>
         </is>
       </c>
-      <c r="E50" s="0" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>友军软分离推力强度</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="0" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>LocalDetourDetourBias</t>
         </is>
       </c>
-      <c r="B51" s="0" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>本地绕行偏置</t>
         </is>
       </c>
-      <c r="C51" s="0" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D51" s="0" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>LocalDetour L/R bias blend</t>
         </is>
       </c>
-      <c r="E51" s="0" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>绕行方向与原期望方向的混合偏置</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="0" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>LocalDetourForwardConeHalfAngleDeg</t>
         </is>
       </c>
-      <c r="B52" s="0" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>本地绕行前向锥半角</t>
         </is>
       </c>
-      <c r="C52" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="D52" s="0" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>Forward block cone half-angle degrees</t>
         </is>
       </c>
-      <c r="E52" s="0" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>判定前方友军阻挡的圆锥半角（度）</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="0" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>BossAdvanceArriveRadius</t>
         </is>
       </c>
-      <c r="B53" s="0" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Boss推进到达半径</t>
         </is>
       </c>
-      <c r="C53" s="0" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D53" s="0" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>BossPoint advance arrive radius</t>
         </is>
       </c>
-      <c r="E53" s="0" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>目标链耗尽后推进Boss点的到达半径</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="0" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>EngageStickHysteresisMargin</t>
         </is>
       </c>
-      <c r="B54" s="0" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>接战粘滞余量</t>
         </is>
       </c>
-      <c r="C54" s="0" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D54" s="0" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>Engage sticky retarget hysteresis</t>
         </is>
       </c>
-      <c r="E54" s="0" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>接战粘滞：新目标需更近超过本余量才换目标</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="0" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>PushMapSpawnMinSampleDistance</t>
         </is>
       </c>
-      <c r="B55" s="0" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>刷怪散布最小采样距</t>
         </is>
       </c>
-      <c r="C55" s="0" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D55" s="0" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>PushMap spawn min sample distance</t>
         </is>
       </c>
-      <c r="E55" s="0" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>刷怪散布环形采样的最小间距</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="0" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>PushMapSpawnSampleDistanceBodyMul</t>
         </is>
       </c>
-      <c r="B56" s="0" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>刷怪散布体半径倍数</t>
         </is>
       </c>
-      <c r="C56" s="0" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D56" s="0" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>Spawn sample distance = max(min</t>
         </is>
       </c>
-      <c r="E56" s="0" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="0" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>PushMapSpawnLeashSlack</t>
         </is>
       </c>
-      <c r="B57" s="0" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>刷怪拴绳松弛</t>
         </is>
       </c>
-      <c r="C57" s="0" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D57" s="0" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>NavMesh sample leash slack</t>
         </is>
       </c>
-      <c r="E57" s="0" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>刷怪SamplePosition相对基点的拴绳松弛</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="0" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>PushMapSpawnAbsoluteLeashFloor</t>
         </is>
       </c>
-      <c r="B58" s="0" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>刷怪绝对拴绳下限</t>
         </is>
       </c>
-      <c r="C58" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" s="0" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>Absolute leash floor</t>
         </is>
       </c>
-      <c r="E58" s="0" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>刷怪绝对拴绳距离下限</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="0" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>PushMapSpawnAbsoluteLeashBodyMul</t>
         </is>
       </c>
-      <c r="B59" s="0" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>刷怪绝对拴绳体倍数</t>
         </is>
       </c>
-      <c r="C59" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="D59" s="0" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>Absolute leash = max(floor</t>
         </is>
       </c>
-      <c r="E59" s="0" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="0" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>DeathKnockbackRatioCoeff</t>
         </is>
       </c>
-      <c r="B60" s="0" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>死亡击飞比例系数</t>
         </is>
       </c>
-      <c r="C60" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D60" s="0" t="inlineStr">
-        <is>
-          <t>Knockback raw=(MaxHp/OutgoingDamage)*Coeff</t>
-        </is>
-      </c>
-      <c r="E60" s="0" t="inlineStr">
-        <is>
-          <t>击飞距离raw=(MaxHp/OutgoingDamage)×本系数；再clamp到Min/Max</t>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Knockback raw=(OutgoingDamage/MaxHp)*Coeff</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="0" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>DeathKnockbackMinDistance</t>
         </is>
       </c>
-      <c r="B61" s="0" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>死亡击飞最小距离</t>
         </is>
       </c>
-      <c r="C61" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D61" s="0" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>Death knockback distance floor</t>
         </is>
       </c>
-      <c r="E61" s="0" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>怪物死亡击飞距离下限（世界单位）</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="0" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>DeathKnockbackMaxDistance</t>
         </is>
       </c>
-      <c r="B62" s="0" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>死亡击飞最大距离</t>
         </is>
       </c>
-      <c r="C62" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D62" s="0" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>Death knockback distance ceiling</t>
         </is>
       </c>
-      <c r="E62" s="0" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DeathDie2KnockbackThreshold</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>死亡Die2击退阈值</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Default Die2; knockback distance&gt;=threshold plays Die; else Die2 (no Die2 falls back to Die)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）</t>
         </is>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,10 +508,8 @@
           <t>普攻主属性倍率</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="C4" t="n">
+        <v>15</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -535,10 +533,8 @@
           <t>攻击速度基础值</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -562,10 +558,8 @@
           <t>攻击速度敏捷除数</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="C6" t="n">
+        <v>60</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -589,10 +583,8 @@
           <t>技能冷却智力除数</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="C7" t="n">
+        <v>30</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -616,10 +608,8 @@
           <t>技能冷却下限</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="C8" t="n">
+        <v>0.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -643,10 +633,8 @@
           <t>血量力量系数</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C9" t="n">
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -670,10 +658,8 @@
           <t>镜头高度</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C10" t="n">
+        <v>18</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -697,10 +683,8 @@
           <t>地图适配Size余量</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="C11" t="n">
+        <v>1.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -724,10 +708,8 @@
           <t>推图开战默认Size</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C12" t="n">
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -751,10 +733,8 @@
           <t>推图布阵默认Size</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="C13" t="n">
+        <v>4.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -778,10 +758,8 @@
           <t>镜头近裁剪面</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="C14" t="n">
+        <v>0.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -805,10 +783,8 @@
           <t>镜头远裁剪面</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="C15" t="n">
+        <v>100</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -832,10 +808,8 @@
           <t>跟随死区半径</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
+      <c r="C16" t="n">
+        <v>0.15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -859,10 +833,8 @@
           <t>跟随平滑时间</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="C17" t="n">
+        <v>0.25</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -886,10 +858,8 @@
           <t>滚轮缩放步进</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="C18" t="n">
+        <v>0.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -913,10 +883,8 @@
           <t>正交Size下限</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="C19" t="n">
+        <v>0.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -940,10 +908,8 @@
           <t>正交Size上限</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="C20" t="n">
+        <v>20</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -967,10 +933,8 @@
           <t>拖拽启动像素阈值</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C21" t="n">
+        <v>4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -994,10 +958,8 @@
           <t>推图镜头预览速度</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="C22" t="n">
+        <v>1.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1021,10 +983,8 @@
           <t>推图镜头预览路点停留</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="C23" t="n">
+        <v>0.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1048,10 +1008,8 @@
           <t>挖坟触发停留</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="C24" t="n">
+        <v>0.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1075,10 +1033,8 @@
           <t>挖坟基础时长</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
+      <c r="C25" t="n">
+        <v>0.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1102,10 +1058,8 @@
           <t>挖坟最短时长</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="C26" t="n">
+        <v>0.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1129,10 +1083,8 @@
           <t>近战攻击位数量</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C27" t="n">
+        <v>12</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1156,10 +1108,8 @@
           <t>远程攻击位数量</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C28" t="n">
+        <v>8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1183,10 +1133,8 @@
           <t>攻击位环半径余量</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+      <c r="C29" t="n">
+        <v>0.05</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1210,10 +1158,8 @@
           <t>攻击位环最小半径</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+      <c r="C30" t="n">
+        <v>0.05</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1237,10 +1183,8 @@
           <t>攻击位重算位移阈值</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="C31" t="n">
+        <v>0.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1264,10 +1208,8 @@
           <t>默认目标体半径</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="C32" t="n">
+        <v>0.35</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1291,10 +1233,8 @@
           <t>命中确认松弛距离</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+      <c r="C33" t="n">
+        <v>0.05</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1318,10 +1258,8 @@
           <t>包围缺口角度</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="C34" t="n">
+        <v>60</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1345,10 +1283,8 @@
           <t>卡死检测窗口</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="C35" t="n">
+        <v>0.5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1372,10 +1308,8 @@
           <t>卡死位移阈值</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="C36" t="n">
+        <v>0.2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1399,10 +1333,8 @@
           <t>卡死停顿时长</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C37" t="n">
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1426,10 +1358,8 @@
           <t>投射物默认命中半径</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="C38" t="n">
+        <v>0.55</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1453,10 +1383,8 @@
           <t>防守胜利阶段经验</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="C39" t="n">
+        <v>100</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1480,10 +1408,8 @@
           <t>流场默认格宽</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="C40" t="n">
+        <v>0.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1507,10 +1433,8 @@
           <t>流场最小格宽</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="C41" t="n">
+        <v>0.25</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1534,10 +1458,8 @@
           <t>流场最大格宽</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="C42" t="n">
+        <v>0.5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1561,10 +1483,8 @@
           <t>群体移动每帧重算上限</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="C43" t="n">
+        <v>50</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1588,10 +1508,8 @@
           <t>群体移动默认体半径</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="C44" t="n">
+        <v>0.1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1615,10 +1533,8 @@
           <t>群体移动到达阈值</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
+      <c r="C45" t="n">
+        <v>0.08</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1642,10 +1558,8 @@
           <t>目标到达默认半径</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C46" t="n">
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1669,10 +1583,8 @@
           <t>攻击位软分离系数</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="C47" t="n">
+        <v>0.35</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1696,10 +1608,8 @@
           <t>软碰撞最大修正速度</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C48" t="n">
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1723,10 +1633,8 @@
           <t>本地绕行探测长度</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C49" t="n">
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1750,10 +1658,8 @@
           <t>本地绕行软分离强度</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
+      <c r="C50" t="n">
+        <v>0.15</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1777,10 +1683,8 @@
           <t>本地绕行偏置</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+      <c r="C51" t="n">
+        <v>0.85</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1804,10 +1708,8 @@
           <t>本地绕行前向锥半角</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="C52" t="n">
+        <v>50</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1831,10 +1733,8 @@
           <t>Boss推进到达半径</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="C53" t="n">
+        <v>0.35</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1858,10 +1758,8 @@
           <t>接战粘滞余量</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
+      <c r="C54" t="n">
+        <v>0.15</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1885,10 +1783,8 @@
           <t>刷怪散布最小采样距</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="C55" t="n">
+        <v>0.75</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1912,10 +1808,8 @@
           <t>刷怪散布体半径倍数</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="C56" t="n">
+        <v>2.5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1939,10 +1833,8 @@
           <t>刷怪拴绳松弛</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="C57" t="n">
+        <v>0.35</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1966,10 +1858,8 @@
           <t>刷怪绝对拴绳下限</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C58" t="n">
+        <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1993,10 +1883,8 @@
           <t>刷怪绝对拴绳体倍数</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C59" t="n">
+        <v>10</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2020,10 +1908,8 @@
           <t>死亡击飞比例系数</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="C60" t="n">
+        <v>0.5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2047,10 +1933,8 @@
           <t>死亡击飞最小距离</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="C61" t="n">
+        <v>0.2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2074,10 +1958,8 @@
           <t>死亡击飞最大距离</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="C62" t="n">
+        <v>5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2101,19 +1983,242 @@
           <t>死亡Die2击退阈值</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C63" t="n">
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Default Die2; knockback distance&gt;=threshold plays Die; else Die2 (no Die2 falls back to Die)</t>
+          <t>Default Die2; distance&gt;=threshold plays Die; corpse smash gate same key</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）</t>
+          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）；尸体砸击门闩同键</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DeathKnockbackPeakHeight</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>死亡击飞抛物线峰值高度</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Corpse projectile Y arc peak (world units)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DeathCorpseSmashDamageMul</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>尸体砸击伤害系数</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DeathCorpseSmashHitRadius</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>尸体砸击命中半径</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>In-flight/landing soft-hit radius</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DeathKnockbackSeconds</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>死亡击飞时长</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Corpse projectile parabolic duration (seconds)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>尸体投射抛物线时长（秒；与t∈[0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DeathDefendCorpseAlphaMul</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Defend尸体透明度系数</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Defend corpse sprite alpha multiplier</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Defend怪/士兵尸体透明度×本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DeathCorpseDarkenMul</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>尸体变暗系数</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Permanent-death corpse RGB multiplier</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DeathFakeDeathCorpseDarkenMul</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>假死尸体变暗系数</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>PushMap fake-death corpse RGB multiplier</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PushMap假死尸体RGB×本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WarriorVisualModelScalePerHit</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>士兵命中体型步进</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WarriorVisualModelScaleMax</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>士兵模型缩放上限</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Clamp VisualModelScale at end of each MagicBook hit apply</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>VisualModelScale每次命中apply末尾夹紧上限</t>
         </is>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1800,573 +1800,623 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PushMapSpawnMinSampleDistance</t>
+          <t>ChaseStuckRetargetSeconds</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>刷怪散布最小采样距</t>
+          <t>追击卡住换目标秒数</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PushMap spawn min sample distance</t>
+          <t>Chase out-of-range stuck force-retarget window seconds</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>刷怪散布环形采样的最小间距</t>
+          <t>追击未进距且位移不足达本秒→强制换目标（排除当前/绕过粘滞）</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PushMapSpawnSampleDistanceBodyMul</t>
+          <t>ChaseStuckRetargetCooldownSeconds</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>刷怪散布体半径倍数</t>
+          <t>追击卡住换目标冷却</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Spawn sample distance = max(min</t>
+          <t>Cooldown after chase-stuck force retarget</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>r*mul)</t>
+          <t>强制换目标后冷却，防A↔B来回甩</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PushMapSpawnLeashSlack</t>
+          <t>PushMapSpawnMinSampleDistance</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>刷怪拴绳松弛</t>
+          <t>刷怪散布最小采样距</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NavMesh sample leash slack</t>
+          <t>PushMap spawn min sample distance</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>刷怪SamplePosition相对基点的拴绳松弛</t>
+          <t>刷怪散布环形采样的最小间距</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PushMapSpawnAbsoluteLeashFloor</t>
+          <t>PushMapSpawnSampleDistanceBodyMul</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳下限</t>
+          <t>刷怪散布体半径倍数</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Absolute leash floor</t>
+          <t>Spawn sample distance = max(min</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳距离下限</t>
+          <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PushMapSpawnAbsoluteLeashBodyMul</t>
+          <t>PushMapSpawnLeashSlack</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳体倍数</t>
+          <t>刷怪拴绳松弛</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>0.35</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Absolute leash = max(floor</t>
+          <t>NavMesh sample leash slack</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>r*mul)</t>
+          <t>刷怪SamplePosition相对基点的拴绳松弛</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DeathKnockbackRatioCoeff</t>
+          <t>PushMapSpawnAbsoluteLeashFloor</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>死亡击飞比例系数</t>
+          <t>刷怪绝对拴绳下限</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Knockback raw=(OutgoingDamage/MaxHp)*Coeff</t>
+          <t>Absolute leash floor</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
+          <t>刷怪绝对拴绳距离下限</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DeathKnockbackMinDistance</t>
+          <t>PushMapSpawnAbsoluteLeashBodyMul</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>死亡击飞最小距离</t>
+          <t>刷怪绝对拴绳体倍数</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Death knockback distance floor</t>
+          <t>Absolute leash = max(floor</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>怪物死亡击飞距离下限（世界单位）</t>
+          <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DeathKnockbackMaxDistance</t>
+          <t>DeathKnockbackRatioCoeff</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>死亡击飞最大距离</t>
+          <t>死亡击飞比例系数</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Death knockback distance ceiling</t>
+          <t>Knockback raw=(OutgoingDamage/MaxHp)*Coeff</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
+          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DeathDie2KnockbackThreshold</t>
+          <t>DeathKnockbackMinDistance</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>死亡Die2击退阈值</t>
+          <t>死亡击飞最小距离</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Default Die2; distance&gt;=threshold plays Die; corpse smash gate same key</t>
+          <t>Death knockback distance floor</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）；尸体砸击门闩同键</t>
+          <t>怪物死亡击飞距离下限（世界单位）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
+          <t>DeathKnockbackMaxDistance</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>死亡击飞方向半角扩散</t>
+          <t>死亡击飞最大距离</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Max yaw offset each side from base knockback direction (degrees)</t>
+          <t>Death knockback distance ceiling</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
+          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DeathKnockbackDirectionRandomStepDegrees</t>
+          <t>DeathDie2KnockbackThreshold</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>死亡击飞方向随机步进</t>
+          <t>死亡Die2击退阈值</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Knockback yaw random granularity (degrees); offset=k*step</t>
+          <t>Default Die2; distance&gt;=threshold plays Die; corpse smash gate same key</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
+          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）；尸体砸击门闩同键</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DeathKnockbackPeakHeight</t>
+          <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>死亡击飞抛物线峰值高度</t>
+          <t>死亡击飞方向半角扩散</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1.2</v>
+        <v>30</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Corpse projectile Y arc peak (world units)</t>
+          <t>Max yaw offset each side from base knockback direction (degrees)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
+          <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DeathCorpseSmashDamageMul</t>
+          <t>DeathKnockbackDirectionRandomStepDegrees</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>尸体砸击伤害系数</t>
+          <t>死亡击飞方向随机步进</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
+          <t>Knockback yaw random granularity (degrees); offset=k*step</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
+          <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DeathCorpseSmashHitRadius</t>
+          <t>DeathKnockbackPeakHeight</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>尸体砸击命中半径</t>
+          <t>死亡击飞抛物线峰值高度</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.55</v>
+        <v>1.2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>In-flight/landing soft-hit radius</t>
+          <t>Corpse projectile Y arc peak (world units)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
+          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DeathKnockbackSeconds</t>
+          <t>DeathCorpseSmashDamageMul</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>死亡击飞时长</t>
+          <t>尸体砸击伤害系数</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Corpse projectile parabolic duration (seconds)</t>
+          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>尸体投射抛物线时长（秒；与t∈[0,1]对齐）</t>
+          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowAlphaMul</t>
+          <t>DeathCorpseSmashHitRadius</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影透明度</t>
+          <t>尸体砸击命中半径</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
+          <t>In-flight/landing soft-hit radius</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
+          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowScaleMin</t>
+          <t>DeathKnockbackSeconds</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影最小缩放</t>
+          <t>死亡击飞时长</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Min shadow diameter scale at ground height (0-1)</t>
+          <t>Corpse projectile parabolic duration (seconds)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
+          <t>尸体投射抛物线时长（秒；与t∈[0,1]对齐）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowBaseRadiusMul</t>
+          <t>DeathKnockbackShadowAlphaMul</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影基准半径倍率</t>
+          <t>击飞腾空地面黑影透明度</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
+          <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
+          <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DeathDefendCorpseAlphaMul</t>
+          <t>DeathKnockbackShadowScaleMin</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Defend尸体透明度系数</t>
+          <t>击飞腾空地面黑影最小缩放</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.85</v>
+        <v>0.35</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Defend corpse sprite alpha multiplier</t>
+          <t>Min shadow diameter scale at ground height (0-1)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Defend怪/士兵尸体透明度×本值</t>
+          <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DeathCorpseDarkenMul</t>
+          <t>DeathKnockbackShadowBaseRadiusMul</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>尸体变暗系数</t>
+          <t>击飞腾空地面黑影基准半径倍率</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Permanent-death corpse RGB multiplier</t>
+          <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
+          <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DeathFakeDeathCorpseDarkenMul</t>
+          <t>DeathDefendCorpseAlphaMul</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>假死尸体变暗系数</t>
+          <t>Defend尸体透明度系数</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PushMap fake-death corpse RGB multiplier</t>
+          <t>Defend corpse sprite alpha multiplier</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PushMap假死尸体RGB×本值</t>
+          <t>Defend怪/士兵尸体透明度×本值</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>WarriorVisualModelScalePerHit</t>
+          <t>DeathCorpseDarkenMul</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>士兵命中体型步进</t>
+          <t>尸体变暗系数</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.15</v>
+        <v>0.4</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
+          <t>Permanent-death corpse RGB multiplier</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
+          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>DeathFakeDeathCorpseDarkenMul</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>假死尸体变暗系数</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PushMap fake-death corpse RGB multiplier</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PushMap假死尸体RGB×本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>WarriorVisualModelScalePerHit</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>士兵命中体型步进</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>WarriorVisualModelScaleMax</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>士兵模型缩放上限</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="C80" t="n">
         <v>3</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Clamp VisualModelScale at end of each MagicBook hit apply</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>VisualModelScale每次命中apply末尾夹紧上限</t>
         </is>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,462 +1025,462 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DigTriggerDwellSeconds</t>
+          <t>SearchExtractHoldOrthoSizeMin</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>挖坟触发停留</t>
+          <t>搜打撤守点Size下限</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cursor dwell before DigAction starts</t>
+          <t>HoldFraming ortho Size floor (intersect CameraOrthoSizeMin)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
+          <t>HoldFraming 正交 Size 下限（再与 CameraOrthoSizeMin 取交）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BaseDigDuration</t>
+          <t>SearchExtractHoldOrthoSizeMax</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>挖坟基础时长</t>
+          <t>搜打撤守点Size上限</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BaseDigDuration seconds</t>
+          <t>HoldFraming ortho Size ceiling (intersect CameraOrthoSizeMax)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DigActionDuration=max(下限</t>
+          <t>HoldFraming 正交 Size 上限（再与 CameraOrthoSizeMax 取交）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DigActionDurationFloor</t>
+          <t>SearchExtractHoldMaxPanRadius</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>挖坟最短时长</t>
+          <t>守点中心偏移半径</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.1</v>
+        <v>8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Min DigActionDuration seconds</t>
+          <t>Max look-at distance from current Objective world XZ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>单次挖坟最短秒数（公式地板）</t>
+          <t>look-at 距当前 Objective 世界 XZ 最大半径；圈外忠诚兵允许出镜</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AttackSlotMeleeCount</t>
+          <t>SearchExtractHoldViewportPad</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>近战攻击位数量</t>
+          <t>守点视口边垫</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>0.08</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Melee AttackSlot ring slot count</t>
+          <t>Outer viewport pad on four sides (0-0.5)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>近战单位围绕目标可占用的攻击位数量</t>
+          <t>外框四边视口垫（0～0.5）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AttackSlotRangedCount</t>
+          <t>SearchExtractHoldTopHudPad</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>远程攻击位数量</t>
+          <t>守点顶HUD垫</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>0.12</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ranged AttackSlot ring slot count</t>
+          <t>Extra top pad for CountdownBar / CombatIndicator</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>远程单位围绕目标可占用的攻击位数量</t>
+          <t>外框顶边额外垫（CountdownBar / CombatIndicator）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AttackSlotMargin</t>
+          <t>SearchExtractHoldInnerPad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>攻击位环半径余量</t>
+          <t>守点内框垫</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ring radius = reach sum - margin</t>
+          <t>Inner pad; tighten only after all stay inside for dwell</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>攻击位环半径计算时从可达距离减去的余量</t>
+          <t>内框边垫；全体在内框内满滞留才允许收紧</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AttackSlotMinRingRadius</t>
+          <t>SearchExtractHoldZoomInDelaySeconds</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>攻击位环最小半径</t>
+          <t>守点拉近滞留秒</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.05</v>
+        <v>0.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Min AttackSlot ring radius</t>
+          <t>Dwell seconds before allowing Size shrink / recenter</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>攻击位环半径下限</t>
+          <t>内框滞留后才允许减小 Size / 回中</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AttackSlotReclaimMoveThreshold</t>
+          <t>SearchExtractHoldSmoothTimeOut</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>攻击位重算位移阈值</t>
+          <t>守点拉远平滑秒</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Target move distance to recompute slots</t>
+          <t>SmoothDamp when expanding Size / pan-out</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>目标移动超过本距离时重算攻击位</t>
+          <t>Size/中心拉远（扩大）SmoothDamp</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AttackSlotDefaultTargetBodyRadius</t>
+          <t>SearchExtractHoldSmoothTimeIn</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>默认目标体半径</t>
+          <t>守点拉近平滑秒</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fallback target BodyRadius</t>
+          <t>SmoothDamp when tightening; must be &gt; Out</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>缺体外观/怪物半径时的默认目标体半径</t>
+          <t>Size/中心拉近（收紧）SmoothDamp；须大于 Out</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HitConfirmSlack</t>
+          <t>SearchExtractHoldSampleInterval</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>命中确认松弛距离</t>
+          <t>守点采样间隔秒</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HitConfirm range slack</t>
+          <t>Low-frequency viewport AABB sample interval seconds</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
+          <t>视口 AABB 低频采样间隔</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SurroundGapDegrees</t>
+          <t>SearchExtractHoldObjectiveBias</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>包围缺口角度</t>
+          <t>守点中心偏向</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>60</v>
+        <v>0.65</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Surround gap sector degrees</t>
+          <t>look-at = lerp(soldier center, Objective, bias); 1=pin Objective</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
+          <t>look-at = lerp(士兵中心, Objective, bias)；1=钉 Objective</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>StuckDetectWindowSeconds</t>
+          <t>DigTriggerDwellSeconds</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>卡死检测窗口</t>
+          <t>挖坟触发停留</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>StuckHold detect window seconds</t>
+          <t>Cursor dwell before DigAction starts</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>有移动意图但位移不足时的检测窗口秒数</t>
+          <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>StuckDisplacementEpsilon</t>
+          <t>BaseDigDuration</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>卡死位移阈值</t>
+          <t>挖坟基础时长</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>StuckHold displacement epsilon</t>
+          <t>BaseDigDuration seconds</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>检测窗口内XZ位移小于本值则判定卡住</t>
+          <t>DigActionDuration=max(下限</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>StuckHoldSeconds</t>
+          <t>DigActionDurationFloor</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>卡死停顿时长</t>
+          <t>挖坟最短时长</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>StuckHold force-Idle seconds</t>
+          <t>Min DigActionDuration seconds</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>判定卡住后强制Idle的秒数</t>
+          <t>单次挖坟最短秒数（公式地板）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ProjectileDefaultHitRadius</t>
+          <t>AttackSlotMeleeCount</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>投射物默认命中半径</t>
+          <t>近战攻击位数量</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.55</v>
+        <v>12</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Default projectile soft-hit radius</t>
+          <t>Melee AttackSlot ring slot count</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>远程投射物默认软命中半径（表缺列时兜底）</t>
+          <t>近战单位围绕目标可占用的攻击位数量</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DefendVictoryStageExp</t>
+          <t>AttackSlotRangedCount</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>防守胜利阶段经验</t>
+          <t>远程攻击位数量</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Defend victory Demo stage Exp</t>
+          <t>Ranged AttackSlot ring slot count</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Defend清场胜利结算时入账的阶段经验</t>
+          <t>远程单位围绕目标可占用的攻击位数量</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FlowFieldDefaultCellSize</t>
+          <t>AttackSlotMargin</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>流场默认格宽</t>
+          <t>攻击位环半径余量</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FlowField default cell size</t>
+          <t>Ring radius = reach sum - margin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>共享目标流场默认格子边长</t>
+          <t>攻击位环半径计算时从可达距离减去的余量</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FlowFieldMinCellSize</t>
+          <t>AttackSlotMinRingRadius</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>流场最小格宽</t>
+          <t>攻击位环最小半径</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FlowField min cell size</t>
+          <t>Min AttackSlot ring radius</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>流场格宽下限（性能降级时可抬高）</t>
+          <t>攻击位环半径下限</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FlowFieldMaxCellSize</t>
+          <t>AttackSlotReclaimMoveThreshold</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>流场最大格宽</t>
+          <t>攻击位重算位移阈值</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1488,937 +1488,1762 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FlowField max cell size</t>
+          <t>Target move distance to recompute slots</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>流场格宽上限</t>
+          <t>目标移动超过本距离时重算攻击位</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MassMoveMaxRecalcPerFrame</t>
+          <t>AttackSlotDefaultTargetBodyRadius</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>群体移动每帧重算上限</t>
+          <t>默认目标体半径</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
+        <v>0.35</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MassMove/AttackSlot refresh budget per frame</t>
+          <t>Fallback target BodyRadius</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>每帧最多重算路径/攻击位的单位数</t>
+          <t>缺体外观/怪物半径时的默认目标体半径</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MassMoveDefaultAgentRadius</t>
+          <t>HitConfirmSlack</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>群体移动默认体半径</t>
+          <t>命中确认松弛距离</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Default mass-move agent radius</t>
+          <t>HitConfirm range slack</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>群体移动登记时的默认体半径</t>
+          <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MassMoveArriveEpsilon</t>
+          <t>SurroundGapDegrees</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>群体移动到达阈值</t>
+          <t>包围缺口角度</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.08</v>
+        <v>60</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Arrive epsilon for DesiredDestination</t>
+          <t>Surround gap sector degrees</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>到达期望点判定的距离阈值</t>
+          <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MassMoveDefaultObjectiveArriveRadius</t>
+          <t>StuckDetectWindowSeconds</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>目标到达默认半径</t>
+          <t>卡死检测窗口</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Default Objective arrive radius</t>
+          <t>StuckHold detect window seconds</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
+          <t>有移动意图但位移不足时的检测窗口秒数</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MassMoveAttackSlotSeparationScale</t>
+          <t>StuckDisplacementEpsilon</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>攻击位软分离系数</t>
+          <t>卡死位移阈值</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LocalDetour separation scale in AttackSlot</t>
+          <t>StuckHold displacement epsilon</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>处于攻击位气泡时LocalDetour软分离缩放</t>
+          <t>检测窗口内XZ位移小于本值则判定卡住</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SoftCollisionMaxCorrectionSpeed</t>
+          <t>StuckHoldSeconds</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>软碰撞最大修正速度</t>
+          <t>卡死停顿时长</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Soft collision max correction speed</t>
+          <t>StuckHold force-Idle seconds</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>软碰撞位置修正速度上限（单位/秒）</t>
+          <t>判定卡住后强制Idle的秒数</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LocalDetourProbeLength</t>
+          <t>ProjectileDefaultHitRadius</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>本地绕行探测长度</t>
+          <t>投射物默认命中半径</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LocalDetour L/R probe length</t>
+          <t>Default projectile soft-hit radius</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>左右绕行探测射线长度</t>
+          <t>远程投射物默认软命中半径（表缺列时兜底）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LocalDetourSoftSeparationStrength</t>
+          <t>DefendVictoryStageExp</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>本地绕行软分离强度</t>
+          <t>防守胜利阶段经验</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.15</v>
+        <v>100</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LocalDetour soft separation strength</t>
+          <t>Defend victory Demo stage Exp</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>友军软分离推力强度</t>
+          <t>Defend清场胜利结算时入账的阶段经验</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LocalDetourDetourBias</t>
+          <t>FlowFieldDefaultCellSize</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>本地绕行偏置</t>
+          <t>流场默认格宽</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LocalDetour L/R bias blend</t>
+          <t>FlowField default cell size</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>绕行方向与原期望方向的混合偏置</t>
+          <t>共享目标流场默认格子边长</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LocalDetourForwardConeHalfAngleDeg</t>
+          <t>FlowFieldMinCellSize</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>本地绕行前向锥半角</t>
+          <t>流场最小格宽</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>50</v>
+        <v>0.25</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Forward block cone half-angle degrees</t>
+          <t>FlowField min cell size</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>判定前方友军阻挡的圆锥半角（度）</t>
+          <t>流场格宽下限（性能降级时可抬高）</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BossAdvanceArriveRadius</t>
+          <t>FlowFieldMaxCellSize</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Boss推进到达半径</t>
+          <t>流场最大格宽</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BossPoint advance arrive radius</t>
+          <t>FlowField max cell size</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>目标链耗尽后推进Boss点的到达半径</t>
+          <t>流场格宽上限</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EngageStickHysteresisMargin</t>
+          <t>MassMoveMaxRecalcPerFrame</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>接战粘滞余量</t>
+          <t>群体移动每帧重算上限</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.15</v>
+        <v>50</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Engage sticky retarget hysteresis</t>
+          <t>MassMove/AttackSlot refresh budget per frame</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>接战粘滞：新目标需更近超过本余量才换目标</t>
+          <t>每帧最多重算路径/攻击位的单位数</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ChaseStuckRetargetSeconds</t>
+          <t>MassMoveDefaultAgentRadius</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>追击卡住换目标秒数</t>
+          <t>群体移动默认体半径</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Chase out-of-range stuck force-retarget window seconds</t>
+          <t>Default mass-move agent radius</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>追击未进距且位移不足达本秒→强制换目标（排除当前/绕过粘滞）</t>
+          <t>群体移动登记时的默认体半径</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ChaseStuckRetargetCooldownSeconds</t>
+          <t>MassMoveArriveEpsilon</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>追击卡住换目标冷却</t>
+          <t>群体移动到达阈值</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cooldown after chase-stuck force retarget</t>
+          <t>Arrive epsilon for DesiredDestination</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>强制换目标后冷却，防A↔B来回甩</t>
+          <t>到达期望点判定的距离阈值</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PushMapSpawnMinSampleDistance</t>
+          <t>MassMoveDefaultObjectiveArriveRadius</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>刷怪散布最小采样距</t>
+          <t>目标到达默认半径</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PushMap spawn min sample distance</t>
+          <t>Default Objective arrive radius</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>刷怪散布环形采样的最小间距</t>
+          <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PushMapSpawnSampleDistanceBodyMul</t>
+          <t>MassMoveAttackSlotSeparationScale</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>刷怪散布体半径倍数</t>
+          <t>攻击位软分离系数</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2.5</v>
+        <v>0.35</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Spawn sample distance = max(min</t>
+          <t>LocalDetour separation scale in AttackSlot</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>r*mul)</t>
+          <t>处于攻击位气泡时LocalDetour软分离缩放</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PushMapSpawnLeashSlack</t>
+          <t>SoftCollisionMaxCorrectionSpeed</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>刷怪拴绳松弛</t>
+          <t>软碰撞最大修正速度</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.35</v>
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NavMesh sample leash slack</t>
+          <t>Soft collision max correction speed</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>刷怪SamplePosition相对基点的拴绳松弛</t>
+          <t>软碰撞位置修正速度上限（单位/秒）</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PushMapSpawnAbsoluteLeashFloor</t>
+          <t>LocalDetourProbeLength</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳下限</t>
+          <t>本地绕行探测长度</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Absolute leash floor</t>
+          <t>LocalDetour L/R probe length</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳距离下限</t>
+          <t>左右绕行探测射线长度</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PushMapSpawnAbsoluteLeashBodyMul</t>
+          <t>LocalDetourSoftSeparationStrength</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳体倍数</t>
+          <t>本地绕行软分离强度</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Absolute leash = max(floor</t>
+          <t>LocalDetour soft separation strength</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>r*mul)</t>
+          <t>友军软分离推力强度</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DeathKnockbackRatioCoeff</t>
+          <t>LocalDetourDetourBias</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>死亡击飞比例系数</t>
+          <t>本地绕行偏置</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Knockback raw=(OutgoingDamage/MaxHp)*Coeff</t>
+          <t>LocalDetour L/R bias blend</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
+          <t>绕行方向与原期望方向的混合偏置</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DeathKnockbackMinDistance</t>
+          <t>LocalDetourForwardConeHalfAngleDeg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>死亡击飞最小距离</t>
+          <t>本地绕行前向锥半角</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.2</v>
+        <v>50</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Death knockback distance floor</t>
+          <t>Forward block cone half-angle degrees</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>怪物死亡击飞距离下限（世界单位）</t>
+          <t>判定前方友军阻挡的圆锥半角（度）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DeathKnockbackMaxDistance</t>
+          <t>BossAdvanceArriveRadius</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>死亡击飞最大距离</t>
+          <t>Boss推进到达半径</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>0.35</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Death knockback distance ceiling</t>
+          <t>BossPoint advance arrive radius</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
+          <t>目标链耗尽后推进Boss点的到达半径</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DeathDie2KnockbackThreshold</t>
+          <t>EngageStickHysteresisMargin</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>死亡Die2击退阈值</t>
+          <t>接战粘滞余量</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Default Die2; distance&gt;=threshold plays Die; corpse smash gate same key</t>
+          <t>Engage sticky retarget hysteresis</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）；尸体砸击门闩同键</t>
+          <t>接战粘滞：新目标需更近超过本余量才换目标</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
+          <t>ChaseStuckRetargetSeconds</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>死亡击飞方向半角扩散</t>
+          <t>追击卡住换目标秒数</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Max yaw offset each side from base knockback direction (degrees)</t>
+          <t>Chase out-of-range stuck force-retarget window seconds</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
+          <t>追击未进距且位移不足达本秒→强制换目标（排除当前/绕过粘滞）</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DeathKnockbackDirectionRandomStepDegrees</t>
+          <t>ChaseStuckRetargetCooldownSeconds</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>死亡击飞方向随机步进</t>
+          <t>追击卡住换目标冷却</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Knockback yaw random granularity (degrees); offset=k*step</t>
+          <t>Cooldown after chase-stuck force retarget</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
+          <t>强制换目标后冷却，防A↔B来回甩</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DeathKnockbackPeakHeight</t>
+          <t>PushMapSpawnMinSampleDistance</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>死亡击飞抛物线峰值高度</t>
+          <t>刷怪散布最小采样距</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Corpse projectile Y arc peak (world units)</t>
+          <t>PushMap spawn min sample distance</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
+          <t>刷怪散布环形采样的最小间距</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DeathCorpseSmashDamageMul</t>
+          <t>PushMapSpawnSampleDistanceBodyMul</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>尸体砸击伤害系数</t>
+          <t>刷怪散布体半径倍数</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
+          <t>Spawn sample distance = max(min</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
+          <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DeathCorpseSmashHitRadius</t>
+          <t>PushMapSpawnLeashSlack</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>尸体砸击命中半径</t>
+          <t>刷怪拴绳松弛</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>In-flight/landing soft-hit radius</t>
+          <t>NavMesh sample leash slack</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
+          <t>刷怪SamplePosition相对基点的拴绳松弛</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DeathKnockbackSeconds</t>
+          <t>PushMapSpawnAbsoluteLeashFloor</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>死亡击飞时长</t>
+          <t>刷怪绝对拴绳下限</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Corpse projectile parabolic duration (seconds)</t>
+          <t>Absolute leash floor</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>尸体投射抛物线时长（秒；与t∈[0,1]对齐）</t>
+          <t>刷怪绝对拴绳距离下限</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowAlphaMul</t>
+          <t>PushMapSpawnAbsoluteLeashBodyMul</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影透明度</t>
+          <t>刷怪绝对拴绳体倍数</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
+          <t>Absolute leash = max(floor</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
+          <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowScaleMin</t>
+          <t>DeathKnockbackRatioCoeff</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影最小缩放</t>
+          <t>死亡击飞比例系数</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Min shadow diameter scale at ground height (0-1)</t>
+          <t>Knockback raw=(OutgoingDamage/MaxHp)*Coeff</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
+          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowBaseRadiusMul</t>
+          <t>DeathKnockbackMinDistance</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影基准半径倍率</t>
+          <t>死亡击飞最小距离</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
+          <t>Death knockback distance floor</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
+          <t>怪物死亡击飞距离下限（世界单位）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DeathDefendCorpseAlphaMul</t>
+          <t>DeathKnockbackMaxDistance</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Defend尸体透明度系数</t>
+          <t>死亡击飞最大距离</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.85</v>
+        <v>5</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Defend corpse sprite alpha multiplier</t>
+          <t>Death knockback distance ceiling</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Defend怪/士兵尸体透明度×本值</t>
+          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DeathCorpseDarkenMul</t>
+          <t>DeathDie2KnockbackThreshold</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>尸体变暗系数</t>
+          <t>死亡Die2击退阈值</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Permanent-death corpse RGB multiplier</t>
+          <t>Default Die2; distance&gt;=threshold plays Die; corpse smash gate same key</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
+          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）；尸体砸击门闩同键</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DeathFakeDeathCorpseDarkenMul</t>
+          <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>假死尸体变暗系数</t>
+          <t>死亡击飞方向半角扩散</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.7</v>
+        <v>30</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PushMap fake-death corpse RGB multiplier</t>
+          <t>Max yaw offset each side from base knockback direction (degrees)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PushMap假死尸体RGB×本值</t>
+          <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>WarriorVisualModelScalePerHit</t>
+          <t>DeathKnockbackDirectionRandomStepDegrees</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>士兵命中体型步进</t>
+          <t>死亡击飞方向随机步进</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1.15</v>
+        <v>5</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
+          <t>Knockback yaw random granularity (degrees); offset=k*step</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
+          <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>DeathKnockbackPeakHeight</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>死亡击飞抛物线峰值高度</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Corpse projectile Y arc peak (world units)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DeathCorpseSmashDamageMul</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>尸体砸击伤害系数</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DeathCorpseSmashHitRadius</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>尸体砸击命中半径</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>In-flight/landing soft-hit radius</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DeathKnockbackSeconds</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>死亡击飞时长</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Corpse projectile parabolic duration (seconds)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>尸体投射抛物线时长（秒；与t∈[0,1]对齐）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DeathKnockbackShadowAlphaMul</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>击飞腾空地面黑影透明度</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DeathKnockbackShadowScaleMin</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>击飞腾空地面黑影最小缩放</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Min shadow diameter scale at ground height (0-1)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DeathKnockbackShadowBaseRadiusMul</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>击飞腾空地面黑影基准半径倍率</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DeathDefendCorpseAlphaMul</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Defend尸体透明度系数</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Defend corpse sprite alpha multiplier</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Defend怪/士兵尸体透明度×本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DeathCorpseDarkenMul</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>尸体变暗系数</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Permanent-death corpse RGB multiplier</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DeathFakeDeathCorpseDarkenMul</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>假死尸体变暗系数</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>PushMap fake-death corpse RGB multiplier</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PushMap假死尸体RGB×本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>WarriorVisualModelScalePerHit</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>士兵命中体型步进</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>WarriorVisualModelScaleMax</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>士兵模型缩放上限</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C91" t="n">
         <v>3</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Clamp VisualModelScale at end of each MagicBook hit apply</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>VisualModelScale每次命中apply末尾夹紧上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyDropIntervalSeconds</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>自动制造尸骸落下间隔</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Seconds between body-rain drop batches</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>UI-016 StepA：每批次掉落间隔秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AutoMfgDropCountMin</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>自动制造尸骸每批最少</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Min pieces per drop batch</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>StepA 每间隔随机落下件数下限</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AutoMfgDropCountMax</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>自动制造尸骸每批最多</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>5</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Max pieces per drop batch</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>StepA 每间隔随机落下件数上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AutoMfgGravityScale</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>自动制造尸骸重力</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Overlay pixel-physics gravity scale (981 px/s2 x this)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Overlay 像素物理重力倍率（981 px/s² × 本值）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AutoMfgBounciness</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>自动制造尸骸弹性</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Pixel-physics soft bounce on floor / piece hits</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>像素物理落地/互撞弱弹</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AutoMfgFriction</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>自动制造尸骸摩擦</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Pixel-physics horizontal + angular damping</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>像素物理水平阻尼 + 角速度阻尼</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AutoMfgColliderInset</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>自动制造尸骸碰撞内缩</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OBB edge vs fitted sprite size (&lt;1 lets slanted pieces nest)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>OBB 边长相对 Sprite 适配尺寸的比例（&lt;1 使斜角更紧）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AutoMfgSpawnAngleMaxDeg</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>自动制造尸骸落下转角</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>50</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Max abs spawn Z yaw (deg); also scales initial angular velocity</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>落下随机 Z 转角绝对值上限（度）；并作初始角速度尺度</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AutoMfgSpawnJitterXPx</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>自动制造尸骸水平微扰</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>80</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Random spawn X jitter in ref pixels</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>落点相对屏幕中心 X 微扰</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AutoMfgMagicCircleFlashHz</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>自动制造法阵闪红频率</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Magic circle red flash Hz during StepB</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>StepB 法阵红色闪烁 Hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AutoMfgReviveSpawnOffsetYPx</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>自动制造复活出生上偏移</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>400</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Revive spawn Y offset from pile base px</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>问号/士兵出生相对堆底向上像素</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AutoMfgPileFloorYPx</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>自动制造尸骸堆地板 Y</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>-300</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Body pile floor Y in ref pixels</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2D 演出层堆地板相对屏幕中心 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierLandYPx</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>自动制造士兵落地 Y</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>-410</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Revived soldier idle land Y px</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>复活士兵落地相对屏幕中心 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyMaxEdgePx</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>自动制造躯体适配边长</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>49</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>StepA body Image max edge px (~35% of prior 140)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>StepA 躯体 Image 最长边像素（约原 140 的 35%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierMaxEdgePx</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>自动制造士兵固定边长</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>64</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>StepB mystery/soldier Image sizeDelta W/H</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>StepB 问号/士兵 Image sizeDelta 宽高（再 × VisualScale）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowWidthPx</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子宽</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>20</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Oval foot-shadow width ref px</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>复活件脚下椭圆影子宽（参考像素）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowHeightPx</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子高</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>8</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Oval foot-shadow height ref px</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>复活件脚下椭圆影子高（参考像素）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowAlpha</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子透明度</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Foot-shadow black Alpha 0-1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>脚下影子黑色 Alpha（0～1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AutoMfgUseLegacySoldierRow</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>自动制造旧士兵行开关</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1=legacy SoldierScroll conveyor</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1=显示中央传送带旧流程；0=尸骸雨默认</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierVisualScale</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>自动制造士兵视觉缩放</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>8</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Revive piece localScale XYZ</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>复活件 localScale（XYZ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowOffsetYPx</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子相对 Y</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>-40</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Shadow local Y vs soldier center</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>影子相对士兵中心的本地 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyAngleMaxDeg</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>自动制造躯体绝对转角上限</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>270</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Clamp body Z angle abs deg; zero omega at limit</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>躯体 Z 转角夹紧 ±本值；触限清角速度</t>
         </is>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,312 +1025,312 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SearchExtractHoldOrthoSizeMin</t>
+          <t>OffScreenSpawnHintIntroBlinkSeconds</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>搜打撤守点Size下限</t>
+          <t>离屏来袭开场闪红秒</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HoldFraming ortho Size floor (intersect CameraOrthoSizeMin)</t>
+          <t>UI-034: intro red-blink window seconds</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HoldFraming 正交 Size 下限（再与 CameraOrthoSizeMin 取交）</t>
+          <t>UI-034：开场闪红总时长秒</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SearchExtractHoldOrthoSizeMax</t>
+          <t>OffScreenSpawnHintIntroBlinkCount</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>搜打撤守点Size上限</t>
+          <t>离屏来袭开场闪红次数</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HoldFraming ortho Size ceiling (intersect CameraOrthoSizeMax)</t>
+          <t>UI-034: red blink count inside intro window</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HoldFraming 正交 Size 上限（再与 CameraOrthoSizeMax 取交）</t>
+          <t>UI-034：开场窗口内闪红次数</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SearchExtractHoldMaxPanRadius</t>
+          <t>OffScreenSpawnHintHoldSeconds</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>守点中心偏移半径</t>
+          <t>离屏来袭常亮秒</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Max look-at distance from current Objective world XZ</t>
+          <t>UI-034: solid white hold seconds after intro blink</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>look-at 距当前 Objective 世界 XZ 最大半径；圈外忠诚兵允许出镜</t>
+          <t>UI-034：闪红后常亮秒数</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SearchExtractHoldViewportPad</t>
+          <t>OffScreenSpawnHintDisplayScale</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>守点视口边垫</t>
+          <t>离屏来袭显示缩放</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.08</v>
+        <v>1.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Outer viewport pad on four sides (0-0.5)</t>
+          <t>UI-034: icon localScale while visible</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>外框四边视口垫（0～0.5）</t>
+          <t>UI-034：显示期间图标 localScale</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SearchExtractHoldTopHudPad</t>
+          <t>OffScreenSpawnHintEdgeMarginPx</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>守点顶HUD垫</t>
+          <t>离屏来袭边距像素</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.12</v>
+        <v>48</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Extra top pad for CountdownBar / CombatIndicator</t>
+          <t>UI-034: icon center margin from screen edge (ref 1920x1080 px)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>外框顶边额外垫（CountdownBar / CombatIndicator）</t>
+          <t>UI-034：图标中心距参考分辨率屏幕边的像素边距</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SearchExtractHoldInnerPad</t>
+          <t>OffScreenSpawnHintIconSizePx</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>守点内框垫</t>
+          <t>离屏来袭图标边长</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.18</v>
+        <v>72</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Inner pad; tighten only after all stay inside for dwell</t>
+          <t>UI-034: EnemyAttack_1 sizeDelta edge (ref 1920x1080)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>内框边垫；全体在内框内满滞留才允许收紧</t>
+          <t>UI-034：EnemyAttack_1 sizeDelta 边长（参考 1920×1080）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SearchExtractHoldZoomInDelaySeconds</t>
+          <t>SearchExtractHoldOrthoSizeMin</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>守点拉近滞留秒</t>
+          <t>搜打撤守点Size下限</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Dwell seconds before allowing Size shrink / recenter</t>
+          <t>HoldFraming ortho Size floor (intersect CameraOrthoSizeMin)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>内框滞留后才允许减小 Size / 回中</t>
+          <t>HoldFraming 正交 Size 下限（再与 CameraOrthoSizeMin 取交）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SearchExtractHoldSmoothTimeOut</t>
+          <t>SearchExtractHoldOrthoSizeMax</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>守点拉远平滑秒</t>
+          <t>搜打撤守点Size上限</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2</v>
+        <v>8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SmoothDamp when expanding Size / pan-out</t>
+          <t>HoldFraming ortho Size ceiling (intersect CameraOrthoSizeMax)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Size/中心拉远（扩大）SmoothDamp</t>
+          <t>HoldFraming 正交 Size 上限（再与 CameraOrthoSizeMax 取交）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SearchExtractHoldSmoothTimeIn</t>
+          <t>SearchExtractHoldMaxPanRadius</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>守点拉近平滑秒</t>
+          <t>守点中心偏移半径</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.55</v>
+        <v>8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SmoothDamp when tightening; must be &gt; Out</t>
+          <t>Max look-at distance from current Objective world XZ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Size/中心拉近（收紧）SmoothDamp；须大于 Out</t>
+          <t>look-at 距当前 Objective 世界 XZ 最大半径；圈外忠诚兵允许出镜</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SearchExtractHoldSampleInterval</t>
+          <t>SearchExtractHoldViewportPad</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>守点采样间隔秒</t>
+          <t>守点视口边垫</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Low-frequency viewport AABB sample interval seconds</t>
+          <t>Outer viewport pad on four sides (0-0.5)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>视口 AABB 低频采样间隔</t>
+          <t>外框四边视口垫（0～0.5）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SearchExtractHoldObjectiveBias</t>
+          <t>SearchExtractHoldTopHudPad</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>守点中心偏向</t>
+          <t>守点顶HUD垫</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.65</v>
+        <v>0.12</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>look-at = lerp(soldier center, Objective, bias); 1=pin Objective</t>
+          <t>Extra top pad for CountdownBar / CombatIndicator</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>look-at = lerp(士兵中心, Objective, bias)；1=钉 Objective</t>
+          <t>外框顶边额外垫（CountdownBar / CombatIndicator）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DigTriggerDwellSeconds</t>
+          <t>SearchExtractHoldInnerPad</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>挖坟触发停留</t>
+          <t>守点内框垫</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cursor dwell before DigAction starts</t>
+          <t>Inner pad; tighten only after all stay inside for dwell</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
+          <t>内框边垫；全体在内框内满滞留才允许收紧</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BaseDigDuration</t>
+          <t>SearchExtractHoldZoomInDelaySeconds</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>挖坟基础时长</t>
+          <t>守点拉近滞留秒</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1338,699 +1338,699 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BaseDigDuration seconds</t>
+          <t>Dwell seconds before allowing Size shrink / recenter</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DigActionDuration=max(下限</t>
+          <t>内框滞留后才允许减小 Size / 回中</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DigActionDurationFloor</t>
+          <t>SearchExtractHoldSmoothTimeOut</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>挖坟最短时长</t>
+          <t>守点拉远平滑秒</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Min DigActionDuration seconds</t>
+          <t>SmoothDamp when expanding Size / pan-out</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>单次挖坟最短秒数（公式地板）</t>
+          <t>Size/中心拉远（扩大）SmoothDamp</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AttackSlotMeleeCount</t>
+          <t>SearchExtractHoldSmoothTimeIn</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>近战攻击位数量</t>
+          <t>守点拉近平滑秒</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>12</v>
+        <v>0.55</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Melee AttackSlot ring slot count</t>
+          <t>SmoothDamp when tightening; must be &gt; Out</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>近战单位围绕目标可占用的攻击位数量</t>
+          <t>Size/中心拉近（收紧）SmoothDamp；须大于 Out</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AttackSlotRangedCount</t>
+          <t>SearchExtractHoldSampleInterval</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>远程攻击位数量</t>
+          <t>守点采样间隔秒</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>0.2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ranged AttackSlot ring slot count</t>
+          <t>Low-frequency viewport AABB sample interval seconds</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>远程单位围绕目标可占用的攻击位数量</t>
+          <t>视口 AABB 低频采样间隔</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AttackSlotMargin</t>
+          <t>SearchExtractHoldObjectiveBias</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>攻击位环半径余量</t>
+          <t>守点中心偏向</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.05</v>
+        <v>0.65</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ring radius = reach sum - margin</t>
+          <t>look-at = lerp(soldier center, Objective, bias); 1=pin Objective</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>攻击位环半径计算时从可达距离减去的余量</t>
+          <t>look-at = lerp(士兵中心, Objective, bias)；1=钉 Objective</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AttackSlotMinRingRadius</t>
+          <t>DigTriggerDwellSeconds</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>攻击位环最小半径</t>
+          <t>挖坟触发停留</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Min AttackSlot ring radius</t>
+          <t>Cursor dwell before DigAction starts</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>攻击位环半径下限</t>
+          <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AttackSlotReclaimMoveThreshold</t>
+          <t>BaseDigDuration</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>攻击位重算位移阈值</t>
+          <t>挖坟基础时长</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Target move distance to recompute slots</t>
+          <t>BaseDigDuration seconds</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>目标移动超过本距离时重算攻击位</t>
+          <t>DigActionDuration=max(下限</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AttackSlotDefaultTargetBodyRadius</t>
+          <t>DigActionDurationFloor</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>默认目标体半径</t>
+          <t>挖坟最短时长</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fallback target BodyRadius</t>
+          <t>Min DigActionDuration seconds</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>缺体外观/怪物半径时的默认目标体半径</t>
+          <t>单次挖坟最短秒数（公式地板）</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HitConfirmSlack</t>
+          <t>AttackSlotMeleeCount</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>命中确认松弛距离</t>
+          <t>近战攻击位数量</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.05</v>
+        <v>12</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HitConfirm range slack</t>
+          <t>Melee AttackSlot ring slot count</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
+          <t>近战单位围绕目标可占用的攻击位数量</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SurroundGapDegrees</t>
+          <t>AttackSlotRangedCount</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>包围缺口角度</t>
+          <t>远程攻击位数量</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Surround gap sector degrees</t>
+          <t>Ranged AttackSlot ring slot count</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
+          <t>远程单位围绕目标可占用的攻击位数量</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>StuckDetectWindowSeconds</t>
+          <t>AttackSlotMargin</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>卡死检测窗口</t>
+          <t>攻击位环半径余量</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>StuckHold detect window seconds</t>
+          <t>Ring radius = reach sum - margin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>有移动意图但位移不足时的检测窗口秒数</t>
+          <t>攻击位环半径计算时从可达距离减去的余量</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>StuckDisplacementEpsilon</t>
+          <t>AttackSlotMinRingRadius</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>卡死位移阈值</t>
+          <t>攻击位环最小半径</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>StuckHold displacement epsilon</t>
+          <t>Min AttackSlot ring radius</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>检测窗口内XZ位移小于本值则判定卡住</t>
+          <t>攻击位环半径下限</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>StuckHoldSeconds</t>
+          <t>AttackSlotReclaimMoveThreshold</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>卡死停顿时长</t>
+          <t>攻击位重算位移阈值</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>StuckHold force-Idle seconds</t>
+          <t>Target move distance to recompute slots</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>判定卡住后强制Idle的秒数</t>
+          <t>目标移动超过本距离时重算攻击位</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ProjectileDefaultHitRadius</t>
+          <t>AttackSlotDefaultTargetBodyRadius</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>投射物默认命中半径</t>
+          <t>默认目标体半径</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Default projectile soft-hit radius</t>
+          <t>Fallback target BodyRadius</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>远程投射物默认软命中半径（表缺列时兜底）</t>
+          <t>缺体外观/怪物半径时的默认目标体半径</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DefendVictoryStageExp</t>
+          <t>HitConfirmSlack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>防守胜利阶段经验</t>
+          <t>命中确认松弛距离</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>100</v>
+        <v>0.05</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Defend victory Demo stage Exp</t>
+          <t>HitConfirm range slack</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Defend清场胜利结算时入账的阶段经验</t>
+          <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FlowFieldDefaultCellSize</t>
+          <t>SurroundGapDegrees</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>流场默认格宽</t>
+          <t>包围缺口角度</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FlowField default cell size</t>
+          <t>Surround gap sector degrees</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>共享目标流场默认格子边长</t>
+          <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FlowFieldMinCellSize</t>
+          <t>StuckDetectWindowSeconds</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>流场最小格宽</t>
+          <t>卡死检测窗口</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FlowField min cell size</t>
+          <t>StuckHold detect window seconds</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>流场格宽下限（性能降级时可抬高）</t>
+          <t>有移动意图但位移不足时的检测窗口秒数</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FlowFieldMaxCellSize</t>
+          <t>StuckDisplacementEpsilon</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>流场最大格宽</t>
+          <t>卡死位移阈值</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FlowField max cell size</t>
+          <t>StuckHold displacement epsilon</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>流场格宽上限</t>
+          <t>检测窗口内XZ位移小于本值则判定卡住</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MassMoveMaxRecalcPerFrame</t>
+          <t>StuckHoldSeconds</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>群体移动每帧重算上限</t>
+          <t>卡死停顿时长</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MassMove/AttackSlot refresh budget per frame</t>
+          <t>StuckHold force-Idle seconds</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>每帧最多重算路径/攻击位的单位数</t>
+          <t>判定卡住后强制Idle的秒数</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MassMoveDefaultAgentRadius</t>
+          <t>ProjectileDefaultHitRadius</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>群体移动默认体半径</t>
+          <t>投射物默认命中半径</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Default mass-move agent radius</t>
+          <t>Default projectile soft-hit radius</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>群体移动登记时的默认体半径</t>
+          <t>远程投射物默认软命中半径（表缺列时兜底）</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MassMoveArriveEpsilon</t>
+          <t>DefendVictoryStageExp</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>群体移动到达阈值</t>
+          <t>防守胜利阶段经验</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.08</v>
+        <v>100</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Arrive epsilon for DesiredDestination</t>
+          <t>Defend victory Demo stage Exp</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>到达期望点判定的距离阈值</t>
+          <t>Defend清场胜利结算时入账的阶段经验</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MassMoveDefaultObjectiveArriveRadius</t>
+          <t>FlowFieldDefaultCellSize</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>目标到达默认半径</t>
+          <t>流场默认格宽</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Default Objective arrive radius</t>
+          <t>FlowField default cell size</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
+          <t>共享目标流场默认格子边长</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MassMoveAttackSlotSeparationScale</t>
+          <t>FlowFieldMinCellSize</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>攻击位软分离系数</t>
+          <t>流场最小格宽</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LocalDetour separation scale in AttackSlot</t>
+          <t>FlowField min cell size</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>处于攻击位气泡时LocalDetour软分离缩放</t>
+          <t>流场格宽下限（性能降级时可抬高）</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SoftCollisionMaxCorrectionSpeed</t>
+          <t>FlowFieldMaxCellSize</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>软碰撞最大修正速度</t>
+          <t>流场最大格宽</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Soft collision max correction speed</t>
+          <t>FlowField max cell size</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>软碰撞位置修正速度上限（单位/秒）</t>
+          <t>流场格宽上限</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LocalDetourProbeLength</t>
+          <t>MassMoveMaxRecalcPerFrame</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>本地绕行探测长度</t>
+          <t>群体移动每帧重算上限</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LocalDetour L/R probe length</t>
+          <t>MassMove/AttackSlot refresh budget per frame</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>左右绕行探测射线长度</t>
+          <t>每帧最多重算路径/攻击位的单位数</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LocalDetourSoftSeparationStrength</t>
+          <t>MassMoveDefaultAgentRadius</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>本地绕行软分离强度</t>
+          <t>群体移动默认体半径</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LocalDetour soft separation strength</t>
+          <t>Default mass-move agent radius</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>友军软分离推力强度</t>
+          <t>群体移动登记时的默认体半径</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LocalDetourDetourBias</t>
+          <t>MassMoveArriveEpsilon</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>本地绕行偏置</t>
+          <t>群体移动到达阈值</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.85</v>
+        <v>0.08</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LocalDetour L/R bias blend</t>
+          <t>Arrive epsilon for DesiredDestination</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>绕行方向与原期望方向的混合偏置</t>
+          <t>到达期望点判定的距离阈值</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LocalDetourForwardConeHalfAngleDeg</t>
+          <t>MassMoveDefaultObjectiveArriveRadius</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>本地绕行前向锥半角</t>
+          <t>目标到达默认半径</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Forward block cone half-angle degrees</t>
+          <t>Default Objective arrive radius</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>判定前方友军阻挡的圆锥半角（度）</t>
+          <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BossAdvanceArriveRadius</t>
+          <t>MassMoveAttackSlotSeparationScale</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Boss推进到达半径</t>
+          <t>攻击位软分离系数</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2038,49 +2038,49 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BossPoint advance arrive radius</t>
+          <t>LocalDetour separation scale in AttackSlot</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>目标链耗尽后推进Boss点的到达半径</t>
+          <t>处于攻击位气泡时LocalDetour软分离缩放</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EngageStickHysteresisMargin</t>
+          <t>SoftCollisionMaxCorrectionSpeed</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>接战粘滞余量</t>
+          <t>软碰撞最大修正速度</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.15</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Engage sticky retarget hysteresis</t>
+          <t>Soft collision max correction speed</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>接战粘滞：新目标需更近超过本余量才换目标</t>
+          <t>软碰撞位置修正速度上限（单位/秒）</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ChaseStuckRetargetSeconds</t>
+          <t>LocalDetourProbeLength</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>追击卡住换目标秒数</t>
+          <t>本地绕行探测长度</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2088,99 +2088,99 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Chase out-of-range stuck force-retarget window seconds</t>
+          <t>LocalDetour L/R probe length</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>追击未进距且位移不足达本秒→强制换目标（排除当前/绕过粘滞）</t>
+          <t>左右绕行探测射线长度</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ChaseStuckRetargetCooldownSeconds</t>
+          <t>LocalDetourSoftSeparationStrength</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>追击卡住换目标冷却</t>
+          <t>本地绕行软分离强度</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cooldown after chase-stuck force retarget</t>
+          <t>LocalDetour soft separation strength</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>强制换目标后冷却，防A↔B来回甩</t>
+          <t>友军软分离推力强度</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PushMapSpawnMinSampleDistance</t>
+          <t>LocalDetourDetourBias</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>刷怪散布最小采样距</t>
+          <t>本地绕行偏置</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PushMap spawn min sample distance</t>
+          <t>LocalDetour L/R bias blend</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>刷怪散布环形采样的最小间距</t>
+          <t>绕行方向与原期望方向的混合偏置</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PushMapSpawnSampleDistanceBodyMul</t>
+          <t>LocalDetourForwardConeHalfAngleDeg</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>刷怪散布体半径倍数</t>
+          <t>本地绕行前向锥半角</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2.5</v>
+        <v>50</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Spawn sample distance = max(min</t>
+          <t>Forward block cone half-angle degrees</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>r*mul)</t>
+          <t>判定前方友军阻挡的圆锥半角（度）</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PushMapSpawnLeashSlack</t>
+          <t>BossAdvanceArriveRadius</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>刷怪拴绳松弛</t>
+          <t>Boss推进到达半径</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2188,1060 +2188,1260 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NavMesh sample leash slack</t>
+          <t>BossPoint advance arrive radius</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>刷怪SamplePosition相对基点的拴绳松弛</t>
+          <t>目标链耗尽后推进Boss点的到达半径</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PushMapSpawnAbsoluteLeashFloor</t>
+          <t>EngageStickHysteresisMargin</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳下限</t>
+          <t>接战粘滞余量</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>0.15</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Absolute leash floor</t>
+          <t>Engage sticky retarget hysteresis</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳距离下限</t>
+          <t>接战粘滞：新目标需更近超过本余量才换目标</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PushMapSpawnAbsoluteLeashBodyMul</t>
+          <t>ChaseStuckRetargetSeconds</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳体倍数</t>
+          <t>追击卡住换目标秒数</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Absolute leash = max(floor</t>
+          <t>Chase out-of-range stuck force-retarget window seconds</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>r*mul)</t>
+          <t>追击未进距且位移不足达本秒→强制换目标（排除当前/绕过粘滞）</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DeathKnockbackRatioCoeff</t>
+          <t>ChaseStuckRetargetCooldownSeconds</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>死亡击飞比例系数</t>
+          <t>追击卡住换目标冷却</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Knockback raw=(OutgoingDamage/MaxHp)*Coeff</t>
+          <t>Cooldown after chase-stuck force retarget</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
+          <t>强制换目标后冷却，防A↔B来回甩</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DeathKnockbackMinDistance</t>
+          <t>PushMapSpawnMinSampleDistance</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>死亡击飞最小距离</t>
+          <t>刷怪散布最小采样距</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Death knockback distance floor</t>
+          <t>PushMap spawn min sample distance</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>怪物死亡击飞距离下限（世界单位）</t>
+          <t>刷怪散布环形采样的最小间距</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DeathKnockbackMaxDistance</t>
+          <t>PushMapSpawnSampleDistanceBodyMul</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>死亡击飞最大距离</t>
+          <t>刷怪散布体半径倍数</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Death knockback distance ceiling</t>
+          <t>Spawn sample distance = max(min</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
+          <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DeathDie2KnockbackThreshold</t>
+          <t>PushMapSpawnLeashSlack</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>死亡Die2击退阈值</t>
+          <t>刷怪拴绳松弛</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Default Die2; distance&gt;=threshold plays Die; corpse smash gate same key</t>
+          <t>NavMesh sample leash slack</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）；尸体砸击门闩同键</t>
+          <t>刷怪SamplePosition相对基点的拴绳松弛</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
+          <t>PushMapSpawnAbsoluteLeashFloor</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>死亡击飞方向半角扩散</t>
+          <t>刷怪绝对拴绳下限</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Max yaw offset each side from base knockback direction (degrees)</t>
+          <t>Absolute leash floor</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
+          <t>刷怪绝对拴绳距离下限</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DeathKnockbackDirectionRandomStepDegrees</t>
+          <t>PushMapSpawnAbsoluteLeashBodyMul</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>死亡击飞方向随机步进</t>
+          <t>刷怪绝对拴绳体倍数</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Knockback yaw random granularity (degrees); offset=k*step</t>
+          <t>Absolute leash = max(floor</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
+          <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DeathKnockbackPeakHeight</t>
+          <t>DeathKnockbackRatioCoeff</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>死亡击飞抛物线峰值高度</t>
+          <t>死亡击飞比例系数</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Corpse projectile Y arc peak (world units)</t>
+          <t>Knockback raw=(OutgoingDamage/MaxHp)*Coeff</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
+          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DeathCorpseSmashDamageMul</t>
+          <t>DeathKnockbackMinDistance</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>尸体砸击伤害系数</t>
+          <t>死亡击飞最小距离</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
+          <t>Death knockback distance floor</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
+          <t>怪物死亡击飞距离下限（世界单位）</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DeathCorpseSmashHitRadius</t>
+          <t>DeathKnockbackMaxDistance</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>尸体砸击命中半径</t>
+          <t>死亡击飞最大距离</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.55</v>
+        <v>5</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>In-flight/landing soft-hit radius</t>
+          <t>Death knockback distance ceiling</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
+          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DeathKnockbackSeconds</t>
+          <t>DeathDie2KnockbackThreshold</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>死亡击飞时长</t>
+          <t>死亡Die2击退阈值</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Corpse projectile parabolic duration (seconds)</t>
+          <t>Default Die2; distance&gt;=threshold plays Die; corpse smash gate same key</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>尸体投射抛物线时长（秒；与t∈[0,1]对齐）</t>
+          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）；尸体砸击门闩同键</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowAlphaMul</t>
+          <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影透明度</t>
+          <t>死亡击飞方向半角扩散</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.6</v>
+        <v>30</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
+          <t>Max yaw offset each side from base knockback direction (degrees)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
+          <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowScaleMin</t>
+          <t>DeathKnockbackDirectionRandomStepDegrees</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影最小缩放</t>
+          <t>死亡击飞方向随机步进</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.35</v>
+        <v>5</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Min shadow diameter scale at ground height (0-1)</t>
+          <t>Knockback yaw random granularity (degrees); offset=k*step</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
+          <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowBaseRadiusMul</t>
+          <t>DeathKnockbackPeakHeight</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影基准半径倍率</t>
+          <t>死亡击飞抛物线峰值高度</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
+          <t>Corpse projectile Y arc peak (world units)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
+          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DeathDefendCorpseAlphaMul</t>
+          <t>DeathCorpseSmashDamageMul</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Defend尸体透明度系数</t>
+          <t>尸体砸击伤害系数</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Defend corpse sprite alpha multiplier</t>
+          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Defend怪/士兵尸体透明度×本值</t>
+          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DeathCorpseDarkenMul</t>
+          <t>DeathCorpseSmashHitRadius</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>尸体变暗系数</t>
+          <t>尸体砸击命中半径</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Permanent-death corpse RGB multiplier</t>
+          <t>In-flight/landing soft-hit radius</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
+          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DeathFakeDeathCorpseDarkenMul</t>
+          <t>DeathKnockbackSeconds</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>假死尸体变暗系数</t>
+          <t>死亡击飞时长</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PushMap fake-death corpse RGB multiplier</t>
+          <t>Corpse projectile parabolic duration (seconds)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PushMap假死尸体RGB×本值</t>
+          <t>尸体投射抛物线时长（秒；与t∈[0,1]对齐）</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>WarriorVisualModelScalePerHit</t>
+          <t>DeathKnockbackShadowAlphaMul</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>士兵命中体型步进</t>
+          <t>击飞腾空地面黑影透明度</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.15</v>
+        <v>0.6</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
+          <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
+          <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>WarriorVisualModelScaleMax</t>
+          <t>DeathKnockbackShadowScaleMin</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>士兵模型缩放上限</t>
+          <t>击飞腾空地面黑影最小缩放</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>0.35</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Clamp VisualModelScale at end of each MagicBook hit apply</t>
+          <t>Min shadow diameter scale at ground height (0-1)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>VisualModelScale每次命中apply末尾夹紧上限</t>
+          <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AutoMfgBodyDropIntervalSeconds</t>
+          <t>DeathKnockbackShadowBaseRadiusMul</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>自动制造尸骸落下间隔</t>
+          <t>击飞腾空地面黑影基准半径倍率</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Seconds between body-rain drop batches</t>
+          <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UI-016 StepA：每批次掉落间隔秒</t>
+          <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AutoMfgDropCountMin</t>
+          <t>DeathDefendCorpseAlphaMul</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>自动制造尸骸每批最少</t>
+          <t>Defend尸体透明度系数</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>0.85</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Min pieces per drop batch</t>
+          <t>Defend corpse sprite alpha multiplier</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>StepA 每间隔随机落下件数下限</t>
+          <t>Defend怪/士兵尸体透明度×本值</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AutoMfgDropCountMax</t>
+          <t>DeathCorpseDarkenMul</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>自动制造尸骸每批最多</t>
+          <t>尸体变暗系数</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Max pieces per drop batch</t>
+          <t>Permanent-death corpse RGB multiplier</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>StepA 每间隔随机落下件数上限</t>
+          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AutoMfgGravityScale</t>
+          <t>DeathFakeDeathCorpseDarkenMul</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>自动制造尸骸重力</t>
+          <t>假死尸体变暗系数</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Overlay pixel-physics gravity scale (981 px/s2 x this)</t>
+          <t>PushMap fake-death corpse RGB multiplier</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Overlay 像素物理重力倍率（981 px/s² × 本值）</t>
+          <t>PushMap假死尸体RGB×本值</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AutoMfgBounciness</t>
+          <t>WarriorVisualModelScalePerHit</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>自动制造尸骸弹性</t>
+          <t>士兵命中体型步进</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.15</v>
+        <v>1.15</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Pixel-physics soft bounce on floor / piece hits</t>
+          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>像素物理落地/互撞弱弹</t>
+          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AutoMfgFriction</t>
+          <t>WarriorVisualModelScaleMax</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>自动制造尸骸摩擦</t>
+          <t>士兵模型缩放上限</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Pixel-physics horizontal + angular damping</t>
+          <t>Clamp VisualModelScale at end of each MagicBook hit apply</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>像素物理水平阻尼 + 角速度阻尼</t>
+          <t>VisualModelScale每次命中apply末尾夹紧上限</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AutoMfgColliderInset</t>
+          <t>AutoMfgBodyDropIntervalSeconds</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>自动制造尸骸碰撞内缩</t>
+          <t>自动制造尸骸落下间隔</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.72</v>
+        <v>0.3</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>OBB edge vs fitted sprite size (&lt;1 lets slanted pieces nest)</t>
+          <t>Seconds between body-rain drop batches</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OBB 边长相对 Sprite 适配尺寸的比例（&lt;1 使斜角更紧）</t>
+          <t>UI-016 StepA：每批次掉落间隔秒</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AutoMfgSpawnAngleMaxDeg</t>
+          <t>AutoMfgDropCountMin</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>自动制造尸骸落下转角</t>
+          <t>自动制造尸骸每批最少</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Max abs spawn Z yaw (deg); also scales initial angular velocity</t>
+          <t>Min pieces per drop batch</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>落下随机 Z 转角绝对值上限（度）；并作初始角速度尺度</t>
+          <t>StepA 每间隔随机落下件数下限</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AutoMfgSpawnJitterXPx</t>
+          <t>AutoMfgDropCountMax</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>自动制造尸骸水平微扰</t>
+          <t>自动制造尸骸每批最多</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Random spawn X jitter in ref pixels</t>
+          <t>Max pieces per drop batch</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>落点相对屏幕中心 X 微扰</t>
+          <t>StepA 每间隔随机落下件数上限</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AutoMfgMagicCircleFlashHz</t>
+          <t>AutoMfgGravityScale</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>自动制造法阵闪红频率</t>
+          <t>自动制造尸骸重力</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Magic circle red flash Hz during StepB</t>
+          <t>Overlay pixel-physics gravity scale (981 px/s2 x this)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>StepB 法阵红色闪烁 Hz</t>
+          <t>Overlay 像素物理重力倍率（981 px/s² × 本值）</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AutoMfgReviveSpawnOffsetYPx</t>
+          <t>AutoMfgBounciness</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>自动制造复活出生上偏移</t>
+          <t>自动制造尸骸弹性</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>400</v>
+        <v>0.15</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Revive spawn Y offset from pile base px</t>
+          <t>Pixel-physics soft bounce on floor / piece hits</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>问号/士兵出生相对堆底向上像素</t>
+          <t>像素物理落地/互撞弱弹</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AutoMfgPileFloorYPx</t>
+          <t>AutoMfgFriction</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>自动制造尸骸堆地板 Y</t>
+          <t>自动制造尸骸摩擦</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-300</v>
+        <v>0.4</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Body pile floor Y in ref pixels</t>
+          <t>Pixel-physics horizontal + angular damping</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2D 演出层堆地板相对屏幕中心 Y</t>
+          <t>像素物理水平阻尼 + 角速度阻尼</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierLandYPx</t>
+          <t>AutoMfgColliderInset</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>自动制造士兵落地 Y</t>
+          <t>自动制造尸骸碰撞内缩</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-410</v>
+        <v>0.72</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Revived soldier idle land Y px</t>
+          <t>OBB edge vs fitted sprite size (&lt;1 lets slanted pieces nest)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>复活士兵落地相对屏幕中心 Y</t>
+          <t>OBB 边长相对 Sprite 适配尺寸的比例（&lt;1 使斜角更紧）</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AutoMfgBodyMaxEdgePx</t>
+          <t>AutoMfgSpawnAngleMaxDeg</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>自动制造躯体适配边长</t>
+          <t>自动制造尸骸落下转角</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>StepA body Image max edge px (~35% of prior 140)</t>
+          <t>Max abs spawn Z yaw (deg); also scales initial angular velocity</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>StepA 躯体 Image 最长边像素（约原 140 的 35%）</t>
+          <t>落下随机 Z 转角绝对值上限（度）；并作初始角速度尺度</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierMaxEdgePx</t>
+          <t>AutoMfgSpawnJitterXPx</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>自动制造士兵固定边长</t>
+          <t>自动制造尸骸水平微扰</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>StepB mystery/soldier Image sizeDelta W/H</t>
+          <t>Random spawn X jitter in ref pixels</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>StepB 问号/士兵 Image sizeDelta 宽高（再 × VisualScale）</t>
+          <t>落点相对屏幕中心 X 微扰</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierShadowWidthPx</t>
+          <t>AutoMfgMagicCircleFlashHz</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>自动制造士兵影子宽</t>
+          <t>自动制造法阵闪红频率</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Oval foot-shadow width ref px</t>
+          <t>Magic circle red flash Hz during StepB</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>复活件脚下椭圆影子宽（参考像素）</t>
+          <t>StepB 法阵红色闪烁 Hz</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierShadowHeightPx</t>
+          <t>AutoMfgMagicCircleYPx</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>自动制造士兵影子高</t>
+          <t>自动制造法阵本地 Y</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>-50</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Oval foot-shadow height ref px</t>
+          <t>MagicCircle anchoredPosition.y vs AmBodyRainLayer</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>复活件脚下椭圆影子高（参考像素）</t>
+          <t>MagicCircle 相对 AmBodyRainLayer 的 anchoredPosition.y</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierShadowAlpha</t>
+          <t>AutoMfgBodyRainLayerYPx</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>自动制造士兵影子透明度</t>
+          <t>自动制造尸骸雨层本地 Y</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.45</v>
+        <v>-340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Foot-shadow black Alpha 0-1</t>
+          <t>AmBodyRainLayer anchoredPosition.y vs PresentationRoot</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>脚下影子黑色 Alpha（0～1）</t>
+          <t>AmBodyRainLayer 相对 PresentationRoot 的 anchoredPosition.y</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AutoMfgUseLegacySoldierRow</t>
+          <t>AutoMfgReviveSpawnOffsetYPx</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>自动制造旧士兵行开关</t>
+          <t>自动制造复活出生上偏移</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1=legacy SoldierScroll conveyor</t>
+          <t>Revive spawn Y offset from pile base px</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1=显示中央传送带旧流程；0=尸骸雨默认</t>
+          <t>问号/士兵出生相对堆底向上像素</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierVisualScale</t>
+          <t>AutoMfgPileFloorYPx</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>自动制造士兵视觉缩放</t>
+          <t>自动制造尸骸堆地板 Y</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>-300</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Revive piece localScale XYZ</t>
+          <t>Body pile floor Y in ref pixels</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>复活件 localScale（XYZ）</t>
+          <t>2D 演出层堆地板相对屏幕中心 Y</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierShadowOffsetYPx</t>
+          <t>AutoMfgSoldierLandYPx</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>自动制造士兵影子相对 Y</t>
+          <t>自动制造士兵落地 Y</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-40</v>
+        <v>-410</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Shadow local Y vs soldier center</t>
+          <t>Revived soldier idle land Y px</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>影子相对士兵中心的本地 Y</t>
+          <t>复活士兵落地相对屏幕中心 Y</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>AutoMfgBodyMaxEdgePx</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>自动制造躯体适配边长</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>49</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>StepA body Image max edge px (~35% of prior 140)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>StepA 躯体 Image 最长边像素（约原 140 的 35%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierMaxEdgePx</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>自动制造士兵固定边长</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>64</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>StepB mystery/soldier Image sizeDelta W/H</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>StepB 问号/士兵 Image sizeDelta 宽高（再 × VisualScale）</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowWidthPx</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子宽</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>20</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Oval foot-shadow width ref px</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>复活件脚下椭圆影子宽（参考像素）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowHeightPx</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子高</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Oval foot-shadow height ref px</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>复活件脚下椭圆影子高（参考像素）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowAlpha</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子透明度</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Foot-shadow black Alpha 0-1</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>脚下影子黑色 Alpha（0～1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>AutoMfgUseLegacySoldierRow</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>自动制造旧士兵行开关</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1=legacy SoldierScroll conveyor</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1=显示中央传送带旧流程；0=尸骸雨默认</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierVisualScale</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>自动制造士兵视觉缩放</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>8</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Revive piece localScale XYZ</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>复活件 localScale（XYZ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowOffsetYPx</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子相对 Y</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>-32</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Shadow local Y vs soldier feet (bottom pivot)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>影子相对士兵脚底（底部 pivot）的本地 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>AutoMfgBodyAngleMaxDeg</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>自动制造躯体绝对转角上限</t>
         </is>
       </c>
-      <c r="C113" t="n">
+      <c r="C121" t="n">
         <v>270</v>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>Clamp body Z angle abs deg; zero omega at limit</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>躯体 Z 转角夹紧 ±本值；触限清角速度</t>
         </is>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3334,16 +3334,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Foot-shadow black Alpha 0-1</t>
+          <t>Foot-shadow black Alpha 0-1; 0=Demo hide</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>脚下影子黑色 Alpha（0～1）</t>
+          <t>脚下影子黑色 Alpha（0～1；0=Demo 隐藏）</t>
         </is>
       </c>
     </row>
@@ -3400,48 +3400,73 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierShadowOffsetYPx</t>
+          <t>AutoMfgSoldierPitchFactor</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>自动制造士兵影子相对 Y</t>
+          <t>自动制造士兵行间距系数</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-32</v>
+        <v>0.5</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Shadow local Y vs soldier feet (bottom pivot)</t>
+          <t>StepB row pitch = MaxEdge x VisualScale x Factor</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>影子相对士兵脚底（底部 pivot）的本地 Y</t>
+          <t>StepB 行间距=MaxEdge×VisualScale×本值（样例0.5→256）</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>AutoMfgSoldierShadowOffsetYPx</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子相对 Y</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>-32</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Shadow local Y vs soldier feet (bottom pivot)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>影子相对士兵脚底（底部 pivot）的本地 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>AutoMfgBodyAngleMaxDeg</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>自动制造躯体绝对转角上限</t>
         </is>
       </c>
-      <c r="C121" t="n">
+      <c r="C122" t="n">
         <v>270</v>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>Clamp body Z angle abs deg; zero omega at limit</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>躯体 Z 转角夹紧 ±本值；触限清角速度</t>
         </is>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,6 +3472,81 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyAbsorbStaggerSeconds</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>自动制造躯体吸入起飞间隔</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>StepB body absorb stagger launch seconds</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>StepB 同兵躯体件错开起飞间隔（秒；随 speed 缩短）</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyAbsorbFlySeconds</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>自动制造躯体吸入飞入时长</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>StepB body absorb fly-to-center seconds</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>StepB 单件飞入谜底视觉中心时长（秒；随 speed 缩短）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyAbsorbFlashHz</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>自动制造躯体吸入闪红频率</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>8</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>StepB body absorb in-flight white-red flash Hz</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>StepB 飞入中 Image 白↔红闪烁 Hz</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
